--- a/Threadsアフィリエイト/A8ネット案件リサーチ.xlsx
+++ b/Threadsアフィリエイト/A8ネット案件リサーチ.xlsx
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="A8案件一覧" displayName="A8案件一覧" ref="A1:AA115" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="A8案件一覧" displayName="A8案件一覧" ref="A1:AA159" headerRowCount="1">
   <autoFilter ref="A1:Z28"/>
   <tableColumns count="26">
     <tableColumn id="1" name="No."/>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA115"/>
+  <dimension ref="A1:AA159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14865,6 +14865,5602 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>ABABA（不採用通知がスカウトに変わる新卒向けサービス）</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ABABA</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>26年卒以下の学生</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I116" s="7" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K116" s="8">
+        <f>IF(OR(F116="",I116=""),"",F116*I116)</f>
+        <v/>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>WEBより登録完了、30日以内にLINE連携完了した学生</t>
+        </is>
+      </c>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
+          <t>メール・電話連絡不可／いたずら・虚偽・重複登録／1世帯2回以上／サービス利用意思のない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q116" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S116" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T116" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U116" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V116" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W116" s="5" t="inlineStr">
+        <is>
+          <t>「不採用通知をスカウトに変える」というユニークな訴求。報酬1,500円と全体でも最低水準、EPC9.9円も低め</t>
+        </is>
+      </c>
+      <c r="X116" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y116" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA116" s="5" t="inlineStr">
+        <is>
+          <t>s00000024702001</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>アットジーピー（atGP）（障害者サポート実績業界No.1）</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ゼネラルパートナーズ</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>障害者向け</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>障害者手帳保有者</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了（本人確認完了）</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="n">
+        <v>0.8097</v>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K117" s="8">
+        <f>IF(OR(F117="",I117=""),"",F117*I117)</f>
+        <v/>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>WEBより会員登録完了、本人確認完了</t>
+        </is>
+      </c>
+      <c r="O117" s="5" t="inlineStr">
+        <is>
+          <t>悪戯・虚偽・不正・重複の申込／お問い合わせフォームからの申込／メールや電話で連絡がつかない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S117" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T117" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U117" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V117" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
+        <is>
+          <t>確定率80.97%と非常に高いが報酬1,500円と低いためEPCは25.7円にとどまる。15年の実績を訴求</t>
+        </is>
+      </c>
+      <c r="X117" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y117" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA117" s="5" t="inlineStr">
+        <is>
+          <t>s00000017969001</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>PR求人市場（在宅ワーク特化型求人サイト）</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>株式会社PR市場</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>BtoB(求人掲載サービス)</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>求人企業・求人サイト運営者（求職者向けではない）</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="n"/>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>求人企業登録6,000円・求人登録9,000円（掲載確定でそれぞれ発生、案件区分により異なる）</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>掲載確定</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K118" s="8">
+        <f>IF(OR(F118="",I118=""),"",F118*I118)</f>
+        <v/>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の掲載確定</t>
+        </is>
+      </c>
+      <c r="O118" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・キャンセル／入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P118" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q118" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S118" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T118" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U118" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V118" s="5" t="inlineStr">
+        <is>
+          <t>要検討（対象がBtoB）</t>
+        </is>
+      </c>
+      <c r="W118" s="5" t="inlineStr">
+        <is>
+          <t>⚠️他の転職エージェント案件と異なり、求職者ではなく求人企業・求人媒体運営者向けのBtoBサービス。本シートの「求職者をアフィリエイトで送客する」文脈とは対象が逆のため、含めるか要検討</t>
+        </is>
+      </c>
+      <c r="X118" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、報酬は区分により複数あり単一値なし）</t>
+        </is>
+      </c>
+      <c r="Y118" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA118" s="5" t="inlineStr">
+        <is>
+          <t>s00000025637001</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>マイナビジョブ20's（20代・第二新卒・既卒向け転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>株式会社マイナビ</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>第二新卒・既卒(20代)</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>20〜29歳</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>新規申込完了</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>申込完了</t>
+        </is>
+      </c>
+      <c r="I119" s="7" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="K119" s="8">
+        <f>IF(OR(F119="",I119=""),"",F119*I119)</f>
+        <v/>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の申込完了／対象地域限定・20〜29歳</t>
+        </is>
+      </c>
+      <c r="O119" s="5" t="inlineStr">
+        <is>
+          <t>入力不備・キャンセル／不正な方や虚偽の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P119" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q119" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R119" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S119" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T119" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U119" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V119" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W119" s="5" t="inlineStr">
+        <is>
+          <t>マイナビグループの20代・第二新卒特化サービス。確定率68.42%・EPC102.04円と堅実</t>
+        </is>
+      </c>
+      <c r="X119" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y119" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA119" s="5" t="inlineStr">
+        <is>
+          <t>s00000027373001</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>IDA（アパレル・ファッションの求人・転職・派遣）</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>株式会社IDA</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>アパレル・ファッション業界</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>20〜50代のアパレル・コスメ業界志望者</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="n"/>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>サービス種別・年収帯で細分化（人材紹介：年収350万円以上28,000円/未満14,000円、契約社員登録：14,728円/8,000円、派遣：1,488円）</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>サービス利用完了（区分による）</t>
+        </is>
+      </c>
+      <c r="I120" s="7" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="K120" s="8">
+        <f>IF(OR(F120="",I120=""),"",F120*I120)</f>
+        <v/>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBエントリー後、キャリアアドバイザーとの面談完了</t>
+        </is>
+      </c>
+      <c r="O120" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・なりすまし・不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P120" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q120" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R120" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S120" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T120" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U120" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V120" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W120" s="5" t="inlineStr">
+        <is>
+          <t>業界21年の実績。報酬体系が複雑（サービス区分・年収帯で異なる）なため単一の報酬額を入力していない点に注意</t>
+        </is>
+      </c>
+      <c r="X120" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、報酬は区分により複数あり単一値なし）</t>
+        </is>
+      </c>
+      <c r="Y120" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA120" s="5" t="inlineStr">
+        <is>
+          <t>s00000023434001</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>アカリクイベント（大学院生・理系学生特化のオンライン就活イベント）</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アカリク</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>新卒・研究職(大学院生・理系)</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>26卒・27卒の大学院生</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>新規イベント参加</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>イベント参加完了</t>
+        </is>
+      </c>
+      <c r="I121" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J121" s="6" t="n"/>
+      <c r="K121" s="8">
+        <f>IF(OR(F121="",I121=""),"",F121*I121)</f>
+        <v/>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のイベント参加完了／26卒・27卒対象</t>
+        </is>
+      </c>
+      <c r="O121" s="5" t="inlineStr">
+        <is>
+          <t>登録情報が明らかに本人と不一致／不正・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q121" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R121" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S121" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T121" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U121" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V121" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W121" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のアカリク就職エージェントの派生イベント型。報酬2,000円と低額だが確定率50%</t>
+        </is>
+      </c>
+      <c r="X121" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y121" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA121" s="5" t="inlineStr">
+        <is>
+          <t>s00000023028004</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>atGP就活エージェント（病気や症状に配慮した学生向け就活サービス）</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ゼネラルパートナーズ</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>障害者向け(学生)</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>大学生・大学院生・専門学校生（障害・症状への配慮希望者）</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K122" s="8">
+        <f>IF(OR(F122="",I122=""),"",F122*I122)</f>
+        <v/>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N122" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O122" s="5" t="inlineStr">
+        <is>
+          <t>悪戯・虚偽・不正の申込／1世帯2回以上の申込／ログインできない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P122" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q122" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R122" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S122" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T122" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U122" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V122" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W122" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のatGP（既存行）の学生・就活版。確定率18.18%・EPC0.88円と低め</t>
+        </is>
+      </c>
+      <c r="X122" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y122" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA122" s="5" t="inlineStr">
+        <is>
+          <t>s00000017969009</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>LIBZ（逆求人型転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>株式会社リブ</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>IT・ハイクラス</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>20代〜40代前半</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I123" s="7" t="n">
+        <v>0.9157</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>207.33</v>
+      </c>
+      <c r="K123" s="8">
+        <f>IF(OR(F123="",I123=""),"",F123*I123)</f>
+        <v/>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了、有効エントリー完了</t>
+        </is>
+      </c>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・いたずら・重複成果・キャンセル／ログイン不可等のASPストラクチャ不可／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q123" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S123" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T123" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U123" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V123" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W123" s="5" t="inlineStr">
+        <is>
+          <t>確定率91.57%・EPC207.33円と高水準。逆求人型（企業からオファーが届く）が特徴</t>
+        </is>
+      </c>
+      <c r="X123" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y123" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA123" s="5" t="inlineStr">
+        <is>
+          <t>s00000015285002</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>はじめての保育士転職サポート（学童保育所専門）</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>株式会社サクシード</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J124" s="6" t="n"/>
+      <c r="K124" s="8">
+        <f>IF(OR(F124="",I124=""),"",F124*I124)</f>
+        <v/>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>約15日</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規（当広告主を初めて利用する方）／WEBより14日以内に電話確認等の資格保有確認完了</t>
+        </is>
+      </c>
+      <c r="O124" s="5" t="inlineStr">
+        <is>
+          <t>イタズラ・利用歴がある場合／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P124" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R124" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S124" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T124" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U124" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V124" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W124" s="5" t="inlineStr">
+        <is>
+          <t>学童保育専門というニッチ特化。確定目安が約15日と他案件より短い。確定率50%、EPCは非表示</t>
+        </is>
+      </c>
+      <c r="X124" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y124" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA124" s="5" t="inlineStr">
+        <is>
+          <t>s00000014574009</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>職人から施工管理エージェント（職人・現場作業員専門の転職支援）</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>建設・職人</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>40歳未満の男性、職人・現場作業員経験者</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>2930</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="n"/>
+      <c r="J125" s="6" t="n"/>
+      <c r="K125" s="8">
+        <f>IF(OR(F125="",I125=""),"",F125*I125)</f>
+        <v/>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N125" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の本人確認完了／40歳未満の男性・職人経験者</t>
+        </is>
+      </c>
+      <c r="O125" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・キャンセル等いたずら／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P125" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q125" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R125" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S125" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T125" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U125" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V125" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W125" s="5" t="inlineStr">
+        <is>
+          <t>職人・現場作業員から施工管理職への転換支援という珍しいニッチ。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X125" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y125" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA125" s="5" t="inlineStr">
+        <is>
+          <t>s00000021947005</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>日本ドライバー人材センター（タクシー・配送・トラック等ドライバー人材紹介）</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Blue_Rocket</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>ドライバー・運輸</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>30〜40代男性中心</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I126" s="7" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="K126" s="8">
+        <f>IF(OR(F126="",I126=""),"",F126*I126)</f>
+        <v/>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に電話またはメールアドレス送信での確認完了</t>
+        </is>
+      </c>
+      <c r="O126" s="5" t="inlineStr">
+        <is>
+          <t>なりすまし・不正／電話番号が確認できない場合／サービス理解不足での申込／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q126" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R126" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S126" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T126" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U126" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V126" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W126" s="5" t="inlineStr">
+        <is>
+          <t>確定率55.55%だがEPC19.53円と低め。日本トップクラスの求人数を訴求</t>
+        </is>
+      </c>
+      <c r="X126" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y126" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA126" s="5" t="inlineStr">
+        <is>
+          <t>s00000026388001</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>ランスタッド 障害者の転職（世界最大級転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>ランスタッド株式会社</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>障害者向け</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>18歳以上、障害者手帳保有者</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>2499</v>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>100.79</v>
+      </c>
+      <c r="K127" s="8">
+        <f>IF(OR(F127="",I127=""),"",F127*I127)</f>
+        <v/>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了、18歳以上の申込</t>
+        </is>
+      </c>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>1世帯2回以上の申込／精神障がいを持つ方、または、就労移行支援事業所等を利用していない方／不正・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q127" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S127" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T127" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U127" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V127" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W127" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のランスタッド（ハイクラス版・既存行）とは別の障害者特化プログラム。確定率96.77%と非常に高い</t>
+        </is>
+      </c>
+      <c r="X127" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y127" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA127" s="5" t="inlineStr">
+        <is>
+          <t>s00000019113003</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>ASSIGN（若手ハイエンド向け転職サイト）</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ASSIGN</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>ハイクラス(若手)</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>22〜35歳</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>7060</v>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I128" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="K128" s="8">
+        <f>IF(OR(F128="",I128=""),"",F128*I128)</f>
+        <v/>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の会員登録完了</t>
+        </is>
+      </c>
+      <c r="O128" s="5" t="inlineStr">
+        <is>
+          <t>個人情報が明らかに不備な場合／なりすまし／虚偽登録・情報の入力／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P128" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q128" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R128" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S128" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T128" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U128" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V128" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W128" s="5" t="inlineStr">
+        <is>
+          <t>確定率100%表示・EPC92.78円。3分間キャリアシミュレーションを訴求する若手ハイエンド特化サイト</t>
+        </is>
+      </c>
+      <c r="X128" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y128" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z128" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA128" s="5" t="inlineStr">
+        <is>
+          <t>s00000019900001</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>リクルートエージェント（転職成功実績No.1）</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>株式会社リクルート</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>総合(全職種)</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>転職希望者全般</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>WEBエントリー・初回来社完了</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>WEBエントリー・初回来社完了</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="n">
+        <v>0.4627</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>175.35</v>
+      </c>
+      <c r="K129" s="8">
+        <f>IF(OR(F129="",I129=""),"",F129*I129)</f>
+        <v/>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>約10日</t>
+        </is>
+      </c>
+      <c r="N129" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBエントリー後、キャリアアドバイザーとの面談完了</t>
+        </is>
+      </c>
+      <c r="O129" s="5" t="inlineStr">
+        <is>
+          <t>サービス利用歴あり／不正・重複・キャンセル等／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P129" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q129" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R129" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S129" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T129" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U129" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V129" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W129" s="5" t="inlineStr">
+        <is>
+          <t>業界最大手・求人数35万件以上を誇るNo.1エージェント。確定率46.27%・EPC175.35円、確定目安が約10日と他案件より短い</t>
+        </is>
+      </c>
+      <c r="X129" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y129" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z129" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA129" s="5" t="inlineStr">
+        <is>
+          <t>s00000001454002</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>カラフルエージェントドライバー（ハローワーク非掲載のレア求人）</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>カラフルキャリア株式会社</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>ドライバー・運輸</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>普通自動車免許保有者、日本国籍または運転免許のある方</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>新規求人紹介申込</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>求人紹介申込完了</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="n">
+        <v>0.8645</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>212.97</v>
+      </c>
+      <c r="K130" s="8">
+        <f>IF(OR(F130="",I130=""),"",F130*I130)</f>
+        <v/>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に本人確認完了</t>
+        </is>
+      </c>
+      <c r="O130" s="5" t="inlineStr">
+        <is>
+          <t>不正・虚偽・いたずら・重複登録／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P130" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q130" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R130" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S130" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T130" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U130" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V130" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W130" s="5" t="inlineStr">
+        <is>
+          <t>確定率86.45%・EPC212.97円と高水準。ハローワーク非掲載の求人を訴求</t>
+        </is>
+      </c>
+      <c r="X130" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y130" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z130" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA130" s="5" t="inlineStr">
+        <is>
+          <t>s00000027599001</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>サロンdeジョブ（美容業界専門求人、掲載数1万件以上）</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ハタラクリエ</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>美容業界</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>20〜40代、美容業界（アイリスト・ネイリスト等）経験者</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="K131" s="8">
+        <f>IF(OR(F131="",I131=""),"",F131*I131)</f>
+        <v/>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N131" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O131" s="5" t="inlineStr">
+        <is>
+          <t>不正・不備・キャンセル／ログイン不可等のASPストラクチャ不可／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P131" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q131" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R131" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S131" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T131" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U131" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V131" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W131" s="5" t="inlineStr">
+        <is>
+          <t>美容業界のニッチ職種（アイリスト・ネイリスト等）特化。確定率25%・EPC65.81円</t>
+        </is>
+      </c>
+      <c r="X131" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y131" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z131" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA131" s="5" t="inlineStr">
+        <is>
+          <t>s00000027048001</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>ケイサーチ（警備員専門求人サイト）</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ケイサーチ</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>警備業</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>18〜69歳</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>求人応募</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>求人応募完了</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="n">
+        <v>0.5416</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>111.49</v>
+      </c>
+      <c r="K132" s="8">
+        <f>IF(OR(F132="",I132=""),"",F132*I132)</f>
+        <v/>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に応募先企業からの電話確認完了</t>
+        </is>
+      </c>
+      <c r="O132" s="5" t="inlineStr">
+        <is>
+          <t>重複登録・虚偽・なりすまし／LINE経由の申込不可／自衛隊員からの申込等除外条件あり／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P132" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q132" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R132" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S132" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T132" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U132" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V132" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W132" s="5" t="inlineStr">
+        <is>
+          <t>警備員特化のニッチ求人サイト。確定率54.16%・EPC111.49円</t>
+        </is>
+      </c>
+      <c r="X132" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y132" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z132" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA132" s="5" t="inlineStr">
+        <is>
+          <t>s00000026677001</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>キャリコン（20代の転職エージェントを複数紹介）</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Crown_Case</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>既卒・第二新卒(20代)</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>20代</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>新規オンライン面談</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>オンライン面談完了</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="K133" s="8">
+        <f>IF(OR(F133="",I133=""),"",F133*I133)</f>
+        <v/>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内にオンライン面談を実施完了</t>
+        </is>
+      </c>
+      <c r="O133" s="5" t="inlineStr">
+        <is>
+          <t>いたずら・不正・重複登録／外国籍の方の登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P133" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q133" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R133" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S133" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T133" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U133" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V133" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W133" s="5" t="inlineStr">
+        <is>
+          <t>複数の転職エージェントを比較紹介するサービス。確定率30.55%だがEPC6.81円と低め</t>
+        </is>
+      </c>
+      <c r="X133" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y133" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z133" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA133" s="5" t="inlineStr">
+        <is>
+          <t>s00000026651001</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>ワンキャリア転職（中の人の声を聞ける転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ワンキャリア</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>ハイクラス</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>20〜30代ハイクラスビジネスパーソン</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了（仮登録後の本会員登録）</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="n">
+        <v>0.9081</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="K134" s="8">
+        <f>IF(OR(F134="",I134=""),"",F134*I134)</f>
+        <v/>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEB登録完了、仮登録後の本会員登録完了</t>
+        </is>
+      </c>
+      <c r="O134" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・不正／ログイン不可のASPストラクチャ不可／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P134" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q134" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R134" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S134" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T134" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U134" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V134" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W134" s="5" t="inlineStr">
+        <is>
+          <t>確定率90.81%と非常に高いがEPC23.26円と報酬額の低さが影響</t>
+        </is>
+      </c>
+      <c r="X134" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y134" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z134" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA134" s="5" t="inlineStr">
+        <is>
+          <t>s00000026465002</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>RSG不動産転職（不動産業界専門の転職支援）</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>RSG</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>不動産業界</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>不動産業界経験者</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>新規カウンセリング</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>カウンセリング完了</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="n">
+        <v>0.9166</v>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>90.56</v>
+      </c>
+      <c r="K135" s="8">
+        <f>IF(OR(F135="",I135=""),"",F135*I135)</f>
+        <v/>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のカウンセリング実施完了</t>
+        </is>
+      </c>
+      <c r="O135" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・キャンセル／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P135" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q135" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R135" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S135" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T135" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U135" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V135" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W135" s="5" t="inlineStr">
+        <is>
+          <t>確定率91.66%と非常に高い。同一広告主のRSG建設転職と系列</t>
+        </is>
+      </c>
+      <c r="X135" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y135" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z135" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA135" s="5" t="inlineStr">
+        <is>
+          <t>s00000021947004</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>RSG建設転職（建設業界専門の転職支援）</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>RSG</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>建設業界</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>建設業界経験者</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>23930</v>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>新規面談完了</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>面談完了</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="n"/>
+      <c r="J136" s="6" t="n"/>
+      <c r="K136" s="8">
+        <f>IF(OR(F136="",I136=""),"",F136*I136)</f>
+        <v/>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M136" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N136" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談完了</t>
+        </is>
+      </c>
+      <c r="O136" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・キャンセル／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P136" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q136" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R136" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S136" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T136" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U136" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V136" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W136" s="5" t="inlineStr">
+        <is>
+          <t>報酬23,930円と高単価。同一広告主RSGの職人から施工管理エージェント（既存行）とは別プログラム。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X136" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y136" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z136" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA136" s="5" t="inlineStr">
+        <is>
+          <t>s00000021947001</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>ファミキャリ（ゲーム業界専門転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アンド・リザーバー</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>ゲーム業界</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>ゲーム業界経験者</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>新規面談完了</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>面談完了</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="n">
+        <v>0.7551</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>577.53</v>
+      </c>
+      <c r="K137" s="8">
+        <f>IF(OR(F137="",I137=""),"",F137*I137)</f>
+        <v/>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N137" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談完了</t>
+        </is>
+      </c>
+      <c r="O137" s="5" t="inlineStr">
+        <is>
+          <t>名前・メールアドレス・電話番号などの不備／不正・重複登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P137" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q137" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R137" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S137" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T137" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U137" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V137" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W137" s="5" t="inlineStr">
+        <is>
+          <t>確定率75.51%・EPC577.53円と高水準。ゲーム業界専門エージェント「ネッキー」を訴求</t>
+        </is>
+      </c>
+      <c r="X137" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y137" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z137" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA137" s="5" t="inlineStr">
+        <is>
+          <t>s00000019744001</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>FoodsLabo（飲食業界特化の採用DXプラットフォーム）</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>株式会社クオレガ</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>飲食業界</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>18〜50歳、飲食業界経験者</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>新規応募</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>応募完了</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>110.76</v>
+      </c>
+      <c r="K138" s="8">
+        <f>IF(OR(F138="",I138=""),"",F138*I138)</f>
+        <v/>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより14日以内の応募完了</t>
+        </is>
+      </c>
+      <c r="O138" s="5" t="inlineStr">
+        <is>
+          <t>いたずら・虚偽／人員不足を理由にした転職活動には利用不可／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P138" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q138" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R138" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S138" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T138" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U138" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V138" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W138" s="5" t="inlineStr">
+        <is>
+          <t>飲食業界特化の採用DXプラットフォーム。確定率30.76%・EPC110.76円</t>
+        </is>
+      </c>
+      <c r="X138" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y138" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z138" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA138" s="5" t="inlineStr">
+        <is>
+          <t>s00000017827002</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>相性転職PersonalFile（相性でマッチングする20代向け転職）</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>株式会社W・Creed</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>未経験・一般(20代)</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>20〜29歳</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>新規面談完了</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>面談完了</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="n"/>
+      <c r="J139" s="6" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="K139" s="8">
+        <f>IF(OR(F139="",I139=""),"",F139*I139)</f>
+        <v/>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N139" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談完了</t>
+        </is>
+      </c>
+      <c r="O139" s="5" t="inlineStr">
+        <is>
+          <t>いたずら・重複・虚偽／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P139" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q139" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R139" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S139" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T139" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U139" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V139" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W139" s="5" t="inlineStr">
+        <is>
+          <t>「相性」でマッチングするというユニークな訴求軸。確定率は非表示、EPC30.25円</t>
+        </is>
+      </c>
+      <c r="X139" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率データなし）</t>
+        </is>
+      </c>
+      <c r="Y139" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z139" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA139" s="5" t="inlineStr">
+        <is>
+          <t>s00000017180047</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>LHH転職エージェント（年収以外にもこだわるハイクラス転職）</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>アデコ株式会社</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>ハイクラス</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>年収600万円以上、25〜55歳</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>427.78</v>
+      </c>
+      <c r="K140" s="8">
+        <f>IF(OR(F140="",I140=""),"",F140*I140)</f>
+        <v/>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M140" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより新規会員登録完了</t>
+        </is>
+      </c>
+      <c r="O140" s="5" t="inlineStr">
+        <is>
+          <t>個人情報の重複・虚偽・不正／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P140" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q140" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R140" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S140" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T140" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U140" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V140" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W140" s="5" t="inlineStr">
+        <is>
+          <t>確定率85.2%・EPC427.78円と高水準。アデコグループのハイクラス特化エージェント</t>
+        </is>
+      </c>
+      <c r="X140" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y140" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z140" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA140" s="5" t="inlineStr">
+        <is>
+          <t>s00000026941002</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>ブラッシュアップジャパン（20代の転職相談所、第二新卒支援）</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>第二新卒(20代)</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>22〜29歳</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="J141" s="6" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="K141" s="8">
+        <f>IF(OR(F141="",I141=""),"",F141*I141)</f>
+        <v/>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N141" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O141" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・不正／サービス利用意思のない登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P141" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q141" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R141" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S141" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T141" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U141" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V141" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W141" s="5" t="inlineStr">
+        <is>
+          <t>確定率33.33%だがEPC15.58円と低め。プログラムIDは画像が不鮮明で要再確認</t>
+        </is>
+      </c>
+      <c r="X141" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、プログラムID要確認）</t>
+        </is>
+      </c>
+      <c r="Y141" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z141" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA141" s="5" t="inlineStr">
+        <is>
+          <t>未確認（画像不鮮明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>ハタラクティブ（フリーター・既卒・第二新卒向け転職支援）</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>レバレジーズ株式会社</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>第二新卒・既卒・フリーター</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>フリーター・既卒・第二新卒</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>新規カウンセリング完了</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>カウンセリング完了</t>
+        </is>
+      </c>
+      <c r="I142" s="7" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K142" s="8">
+        <f>IF(OR(F142="",I142=""),"",F142*I142)</f>
+        <v/>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N142" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のカウンセリング完了</t>
+        </is>
+      </c>
+      <c r="O142" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P142" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q142" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R142" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S142" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T142" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U142" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V142" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W142" s="5" t="inlineStr">
+        <is>
+          <t>確定率62.96%だがEPC16.3円と低め。同一広告主レバレジーズの主力未経験系サービス</t>
+        </is>
+      </c>
+      <c r="X142" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y142" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z142" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA142" s="5" t="inlineStr">
+        <is>
+          <t>s00000011866008</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>キャリアチケット（成長企業特化型転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>レバレジーズ株式会社</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>既卒・第二新卒(20代)</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>24〜34歳既卒・第二新卒</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="6" t="n">
+        <v>223.62</v>
+      </c>
+      <c r="K143" s="8">
+        <f>IF(OR(F143="",I143=""),"",F143*I143)</f>
+        <v/>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M143" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N143" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了、24〜34歳</t>
+        </is>
+      </c>
+      <c r="O143" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・不正利用等スパム的行為／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P143" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q143" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R143" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S143" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T143" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U143" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V143" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W143" s="5" t="inlineStr">
+        <is>
+          <t>確定率100%表示・EPC223.62円と高水準。成長企業への転職支援を訴求</t>
+        </is>
+      </c>
+      <c r="X143" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y143" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z143" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA143" s="5" t="inlineStr">
+        <is>
+          <t>s00000011866027</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>ビズリーチ・キャンパス（大手人気企業の就活）</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ビズリーチ</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>2027年卒予定の大学生</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="n"/>
+      <c r="J144" s="6" t="n"/>
+      <c r="K144" s="8">
+        <f>IF(OR(F144="",I144=""),"",F144*I144)</f>
+        <v/>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
+          <t>約7日</t>
+        </is>
+      </c>
+      <c r="N144" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより2027年卒業予定学生の会員登録完了</t>
+        </is>
+      </c>
+      <c r="O144" s="5" t="inlineStr">
+        <is>
+          <t>「OB/OG訪問のため」以外の内定者への接触が確認された場合／サービス目的外の利用／規約違反の場合</t>
+        </is>
+      </c>
+      <c r="P144" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q144" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R144" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S144" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T144" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U144" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V144" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W144" s="5" t="inlineStr">
+        <is>
+          <t>OB/OG訪問プラットフォーム。確定率・EPCとも非表示、確定目安が約7日と短い</t>
+        </is>
+      </c>
+      <c r="X144" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y144" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z144" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA144" s="5" t="inlineStr">
+        <is>
+          <t>s00000014571003</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>LHH就活エージェント（内定を最短ルートで実現する）</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>アデコ株式会社</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>26,27卒の方</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>3307</v>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>新規本会員登録</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>本会員登録完了</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="J145" s="6" t="n"/>
+      <c r="K145" s="8">
+        <f>IF(OR(F145="",I145=""),"",F145*I145)</f>
+        <v/>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N145" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の本会員登録完了</t>
+        </is>
+      </c>
+      <c r="O145" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・キャンセル・なりすまし／外国籍・メールアドレス不備等／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P145" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q145" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R145" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S145" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T145" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U145" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V145" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W145" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主LHH（ハイクラス版・既存行）の新卒版。確定率66.66%だがEPCは非表示</t>
+        </is>
+      </c>
+      <c r="X145" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y145" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z145" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA145" s="5" t="inlineStr">
+        <is>
+          <t>s00000022498002</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>doda新卒エージェント（完全無料で内定獲得までサポート）</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ベネッセi-キャリア</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>27卒生の方</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="n">
+        <v>0.7213000000000001</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>277.53</v>
+      </c>
+      <c r="K146" s="8">
+        <f>IF(OR(F146="",I146=""),"",F146*I146)</f>
+        <v/>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N146" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O146" s="5" t="inlineStr">
+        <is>
+          <t>不正・申込不備・いたずら／重複登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P146" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q146" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R146" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S146" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T146" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U146" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V146" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W146" s="5" t="inlineStr">
+        <is>
+          <t>確定率72.13%・EPC277.53円と高水準。ベネッセグループの新卒特化サービス</t>
+        </is>
+      </c>
+      <c r="X146" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y146" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z146" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA146" s="5" t="inlineStr">
+        <is>
+          <t>s00000026801001</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>MS-Japan（管理部門特化型エージェント・経理/法務/会計士/税理士）</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>株式会社MS-Japan</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>専門職(管理部門)</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>管理部門経験者・有資格者</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="n"/>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>保有資格による（弁護士・会計士等7,122円／その他3,561円）</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>面談完了</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="J147" s="6" t="n">
+        <v>253.56</v>
+      </c>
+      <c r="K147" s="8">
+        <f>IF(OR(F147="",I147=""),"",F147*I147)</f>
+        <v/>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M147" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N147" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談完了</t>
+        </is>
+      </c>
+      <c r="O147" s="5" t="inlineStr">
+        <is>
+          <t>重複登録・虚偽等サービス対象外／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P147" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q147" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R147" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S147" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T147" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U147" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V147" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W147" s="5" t="inlineStr">
+        <is>
+          <t>確定率69.56%・EPC253.56円と高水準。報酬が保有資格の種別で2段階に分かれる点に注意</t>
+        </is>
+      </c>
+      <c r="X147" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、報酬は資格区分により2値あり単一値なし）</t>
+        </is>
+      </c>
+      <c r="Y147" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z147" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA147" s="5" t="inlineStr">
+        <is>
+          <t>s00000017694001</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>RECRUIT DIRECT SCOUT（リクルートのハイクラス転職サービス）</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>株式会社リクルートダイレクトスカウト</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>ハイクラス</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>年収600万円以上の方</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>新規レジュメ登録</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>レジュメ登録完了</t>
+        </is>
+      </c>
+      <c r="I148" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>385.53</v>
+      </c>
+      <c r="K148" s="8">
+        <f>IF(OR(F148="",I148=""),"",F148*I148)</f>
+        <v/>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了、以下いずれかの登録完了（年収600万円以上等）</t>
+        </is>
+      </c>
+      <c r="O148" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・不正／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P148" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q148" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S148" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T148" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U148" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V148" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W148" s="5" t="inlineStr">
+        <is>
+          <t>リクルートのハイクラス・ヘッドハンティング型サービス。確定率44%・EPC385.53円と高水準</t>
+        </is>
+      </c>
+      <c r="X148" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y148" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z148" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA148" s="5" t="inlineStr">
+        <is>
+          <t>s00000018087001</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>レバジョブ（ドライバーの転職）</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>レバレジーズ株式会社</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>ドライバー・運輸</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>18〜65歳（首都圏の場合21〜65歳）</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>新規無料会員登録完了</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>701.39</v>
+      </c>
+      <c r="K149" s="8">
+        <f>IF(OR(F149="",I149=""),"",F149*I149)</f>
+        <v/>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N149" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了</t>
+        </is>
+      </c>
+      <c r="O149" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・不正利用等スパム的行為／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P149" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q149" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R149" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S149" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T149" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U149" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V149" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W149" s="5" t="inlineStr">
+        <is>
+          <t>確定率83.17%・EPC701.39円と全体でも上位級。ドライバー特化ジャンルの中では突出した数値</t>
+        </is>
+      </c>
+      <c r="X149" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y149" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z149" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA149" s="5" t="inlineStr">
+        <is>
+          <t>s0000011866035</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>FIDIA Agent（人と社風で選ぶ就活エージェント）</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>FIDIA_SOLUTIONS株式会社</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>日本国籍、2027年3月卒業予定</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>3760</v>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>新規無料就活相談申込完了</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>無料就活相談申込完了</t>
+        </is>
+      </c>
+      <c r="I150" s="7" t="n"/>
+      <c r="J150" s="6" t="n"/>
+      <c r="K150" s="8">
+        <f>IF(OR(F150="",I150=""),"",F150*I150)</f>
+        <v/>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に就活相談申込完了</t>
+        </is>
+      </c>
+      <c r="O150" s="5" t="inlineStr">
+        <is>
+          <t>不正・虚偽・いたずら・重複成果／ログインできない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P150" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q150" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R150" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S150" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T150" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U150" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V150" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W150" s="5" t="inlineStr">
+        <is>
+          <t>「人と社風で選ぶ」という訴求軸。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X150" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y150" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z150" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA150" s="5" t="inlineStr">
+        <is>
+          <t>s00000027425001</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>ジール就活エージェント（最短2週間で内定獲得）</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ジールコミュニケーションズ</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>2026〜2027年卒生、既卒3年以内</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録完了</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I151" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>139.13</v>
+      </c>
+      <c r="K151" s="8">
+        <f>IF(OR(F151="",I151=""),"",F151*I151)</f>
+        <v/>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N151" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより無料面談予約完了</t>
+        </is>
+      </c>
+      <c r="O151" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・キャンセル・重複・入力不備／集客方法が不適切な場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P151" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q151" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R151" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S151" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T151" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U151" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V151" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W151" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のジール就職エージェント（既存行、第二新卒版）の新卒版。確定率80%・EPC139.13円</t>
+        </is>
+      </c>
+      <c r="X151" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y151" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z151" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA151" s="5" t="inlineStr">
+        <is>
+          <t>s00000023631002</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>きづく。キャリアコーチング（自分の一歩を後押しするコーチング）</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>株式会社one-recollection</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>キャリアコーチング</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>22歳以上50歳未満</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>新規無料相談</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>無料相談完了</t>
+        </is>
+      </c>
+      <c r="I152" s="7" t="n"/>
+      <c r="J152" s="6" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="K152" s="8">
+        <f>IF(OR(F152="",I152=""),"",F152*I152)</f>
+        <v/>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N152" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の無料相談実施完了</t>
+        </is>
+      </c>
+      <c r="O152" s="5" t="inlineStr">
+        <is>
+          <t>同一人物の重複・なりすまし／サービス利用歴あり／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P152" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q152" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R152" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S152" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T152" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U152" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V152" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W152" s="5" t="inlineStr">
+        <is>
+          <t>「ストレングスファインダー」等を用いたコーチングが特徴。確定率非表示、EPC47.05円</t>
+        </is>
+      </c>
+      <c r="X152" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率データなし）</t>
+        </is>
+      </c>
+      <c r="Y152" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z152" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA152" s="5" t="inlineStr">
+        <is>
+          <t>s00000023026001</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>TECH::BASE（未経験からのIT業界志望学生向けチーム学習型無料プログラム）</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>シンクトワイス株式会社</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>新卒・IT(未経験)</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>27卒、大学・院生</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>新規オンライン説明会参加</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>オンライン説明会参加完了</t>
+        </is>
+      </c>
+      <c r="I153" s="7" t="n"/>
+      <c r="J153" s="6" t="n"/>
+      <c r="K153" s="8">
+        <f>IF(OR(F153="",I153=""),"",F153*I153)</f>
+        <v/>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M153" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N153" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のオンライン説明会参加完了</t>
+        </is>
+      </c>
+      <c r="O153" s="5" t="inlineStr">
+        <is>
+          <t>入力不備・重複登録／連絡がつかない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P153" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q153" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R153" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S153" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T153" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U153" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V153" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W153" s="5" t="inlineStr">
+        <is>
+          <t>IT就活のための無料学習プログラム。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X153" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y153" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z153" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA153" s="5" t="inlineStr">
+        <is>
+          <t>s00000022228003</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>キャリセン就活エージェント（オンライン相談から始まる就活支援）</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>シンクトワイス株式会社</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>27卒生、大学・院生</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>新規面談予約完了または新規面談完了（各15,000円）</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>面談予約完了／面談完了</t>
+        </is>
+      </c>
+      <c r="I154" s="7" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="K154" s="8">
+        <f>IF(OR(F154="",I154=""),"",F154*I154)</f>
+        <v/>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N154" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談予約または面談完了</t>
+        </is>
+      </c>
+      <c r="O154" s="5" t="inlineStr">
+        <is>
+          <t>重複・入力不備・キャンセル／サービス利用意思のない登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P154" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q154" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R154" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S154" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T154" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U154" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V154" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W154" s="5" t="inlineStr">
+        <is>
+          <t>確定率60.66%・EPC367.37円と高水準。同一広告主シンクトワイスのTECH::BASEと系列</t>
+        </is>
+      </c>
+      <c r="X154" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y154" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z154" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA154" s="5" t="inlineStr">
+        <is>
+          <t>s00000022228001</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>アデコの転職支援サービス（正社員転職）</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>アデコ株式会社</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>総合(全職種)</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>20代後半〜、派遣就業経験者含む</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="K155" s="8">
+        <f>IF(OR(F155="",I155=""),"",F155*I155)</f>
+        <v/>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N155" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に登録完了</t>
+        </is>
+      </c>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
+          <t>入力不備・重複・キャンセル・不正／20歳未満の申込／ログイン不可等のASPストラクチャ不可／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P155" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q155" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S155" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T155" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U155" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V155" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W155" s="5" t="inlineStr">
+        <is>
+          <t>アデコグループの正社員転職支援。同一広告主のLHH系（ハイクラス・新卒）とは別の総合版。確定率46.13%・EPC83.72円</t>
+        </is>
+      </c>
+      <c r="X155" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y155" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z155" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA155" s="5" t="inlineStr">
+        <is>
+          <t>s00000026941001</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>リアルエステートWORKS（不動産業界特化型転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>リアルエステートWORKS</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>不動産業界</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>20代〜30代</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I156" s="7" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="K156" s="8">
+        <f>IF(OR(F156="",I156=""),"",F156*I156)</f>
+        <v/>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に登録完了</t>
+        </is>
+      </c>
+      <c r="O156" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・不正・履歴不備／サービス利用意思のない登録／不動産業界経験者以外／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P156" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q156" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R156" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S156" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T156" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U156" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V156" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W156" s="5" t="inlineStr">
+        <is>
+          <t>不動産業界特化。確定率23.52%・EPC132.48円。同一広告主の建設Jobsと系列</t>
+        </is>
+      </c>
+      <c r="X156" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y156" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z156" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA156" s="5" t="inlineStr">
+        <is>
+          <t>s00000023057001</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>建設Jobs（日本最大級・施工管理/建設業界の転職サイト）</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>リアルエステートWORKS</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>建設・施工管理</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>20代〜30代</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="n">
+        <v>0.9431</v>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>455.16</v>
+      </c>
+      <c r="K157" s="8">
+        <f>IF(OR(F157="",I157=""),"",F157*I157)</f>
+        <v/>
+      </c>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N157" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に登録完了</t>
+        </is>
+      </c>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・不正・履歴不備／サービス利用意思のない登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P157" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q157" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S157" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T157" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U157" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V157" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W157" s="5" t="inlineStr">
+        <is>
+          <t>確定率94.31%・EPC455.16円と非常に高水準。同一広告主のリアルエステートWORKSと系列</t>
+        </is>
+      </c>
+      <c r="X157" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y157" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z157" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA157" s="5" t="inlineStr">
+        <is>
+          <t>s00000023057002</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>ユニゾンキャリ転職（IT・Web業界特化の新卒就活エージェント）</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>株式会社コンパス・タウン</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>新卒(IT/Web)</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>大学生等（IT・Web業界志望）</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>7450</v>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="n">
+        <v>0.7877999999999999</v>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>134.22</v>
+      </c>
+      <c r="K158" s="8">
+        <f>IF(OR(F158="",I158=""),"",F158*I158)</f>
+        <v/>
+      </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N158" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に登録完了</t>
+        </is>
+      </c>
+      <c r="O158" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・不正・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P158" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q158" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S158" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T158" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U158" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V158" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W158" s="5" t="inlineStr">
+        <is>
+          <t>既存の「ユニゾンキャリア」系列とは広告主が異なる別サービス（コンパス・タウン運営、新卒特化）。確定率78.78%・EPC134.22円</t>
+        </is>
+      </c>
+      <c r="X158" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y158" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z158" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA158" s="5" t="inlineStr">
+        <is>
+          <t>s00000027320002</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>itk（外食産業・飲食特化型転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アイティーケー</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>飲食業界</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>18歳以上</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>新規無料会員登録</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="K159" s="8">
+        <f>IF(OR(F159="",I159=""),"",F159*I159)</f>
+        <v/>
+      </c>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>約20日</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr">
+        <is>
+          <t>WEBより無料会員登録完了、14日以内の本人確認</t>
+        </is>
+      </c>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>アフィリエイター本人の申込／飲食・関東・関西・中部圏以外／18歳未満の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P159" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q159" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S159" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T159" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U159" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V159" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W159" s="5" t="inlineStr">
+        <is>
+          <t>確定率5%・EPC4.95円と全体でも最低水準。確定目安が約20日</t>
+        </is>
+      </c>
+      <c r="X159" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y159" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z159" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA159" s="5" t="inlineStr">
+        <is>
+          <t>s00000016501001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/Threadsアフィリエイト/A8ネット案件リサーチ.xlsx
+++ b/Threadsアフィリエイト/A8ネット案件リサーチ.xlsx
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="A8案件一覧" displayName="A8案件一覧" ref="A1:AA159" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="A8案件一覧" displayName="A8案件一覧" ref="A1:AA210" headerRowCount="1">
   <autoFilter ref="A1:Z28"/>
   <tableColumns count="26">
     <tableColumn id="1" name="No."/>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA159"/>
+  <dimension ref="A1:AA210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20461,6 +20461,6478 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>猫の手AGENT（20代のうちに人生単位のキャリアを設計）</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>株式会社にゃー</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>既卒・第二新卒(20代)</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>22〜29歳</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>新規無料相談申込</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>無料相談申込完了</t>
+        </is>
+      </c>
+      <c r="I160" s="7" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K160" s="8">
+        <f>IF(OR(F160="",I160=""),"",F160*I160)</f>
+        <v/>
+      </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N160" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の無料相談申込完了／22〜29歳</t>
+        </is>
+      </c>
+      <c r="O160" s="5" t="inlineStr">
+        <is>
+          <t>キャンセル・不正・申込不備・虚偽／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P160" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q160" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S160" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T160" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U160" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V160" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W160" s="5" t="inlineStr">
+        <is>
+          <t>確定率66.66%と高いがEPC5.24円と極端に低い。「人生単位のキャリア設計」を訴求</t>
+        </is>
+      </c>
+      <c r="X160" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y160" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z160" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA160" s="5" t="inlineStr">
+        <is>
+          <t>s00000027632001</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>ミライバ保育（保育士・幼稚園教諭の理想の職場探し）</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>株式会社COMPASS</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士・幼稚園教諭)</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>保育士・幼稚園教諭資格保有者</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>新規求人紹介申込</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>求人紹介申込完了</t>
+        </is>
+      </c>
+      <c r="I161" s="7" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="K161" s="8">
+        <f>IF(OR(F161="",I161=""),"",F161*I161)</f>
+        <v/>
+      </c>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N161" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより求人紹介申込完了</t>
+        </is>
+      </c>
+      <c r="O161" s="5" t="inlineStr">
+        <is>
+          <t>キャンセル・不正・申込不備・虚偽／資格未保有・60歳以上の方／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P161" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q161" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R161" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S161" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T161" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U161" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V161" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W161" s="5" t="inlineStr">
+        <is>
+          <t>確定率81.15%・EPC675.5円と保育士系の中でも高水準</t>
+        </is>
+      </c>
+      <c r="X161" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y161" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z161" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA161" s="5" t="inlineStr">
+        <is>
+          <t>s00000027503001</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>オイシルキャリア（生鮮業界特化の転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>株式会社オイシル</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>生鮮・スーパー業界</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>20代〜50代、日本在住、53歳以下</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>新規面談完了</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>面談完了</t>
+        </is>
+      </c>
+      <c r="I162" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J162" s="6" t="n"/>
+      <c r="K162" s="8">
+        <f>IF(OR(F162="",I162=""),"",F162*I162)</f>
+        <v/>
+      </c>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M162" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N162" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより7日以内に面談完了</t>
+        </is>
+      </c>
+      <c r="O162" s="5" t="inlineStr">
+        <is>
+          <t>不正・申込不備・キャンセル・重複登録／日本国籍以外／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P162" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q162" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R162" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S162" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T162" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U162" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V162" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W162" s="5" t="inlineStr">
+        <is>
+          <t>スーパー・生鮮業界特化という珍しいニッチ。確定率40%、EPCは非表示</t>
+        </is>
+      </c>
+      <c r="X162" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y162" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z162" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA162" s="5" t="inlineStr">
+        <is>
+          <t>s00000027284001</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>みつけあ（パーソル発！介護職特化の転職無料フルサポート）</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>パーソルイノベーション株式会社</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>医療・介護</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>18〜64歳</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="n">
+        <v>0.7843</v>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>1956.52</v>
+      </c>
+      <c r="K163" s="8">
+        <f>IF(OR(F163="",I163=""),"",F163*I163)</f>
+        <v/>
+      </c>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M163" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N163" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O163" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・いたずら・重複成果・キャンセル・不正／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P163" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q163" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R163" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S163" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T163" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U163" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V163" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W163" s="5" t="inlineStr">
+        <is>
+          <t>確定率78.43%・EPC1,956.52円と全体でも最高水準級。パーソルグループの介護特化サービス</t>
+        </is>
+      </c>
+      <c r="X163" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y163" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z163" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA163" s="5" t="inlineStr">
+        <is>
+          <t>s00000026823003</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>イノセル（20代の営業職への転職）</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>イノセル株式会社</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>営業職(20代)</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>22〜29歳</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>新規面談相談申込</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>面談相談申込完了</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="J164" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K164" s="8">
+        <f>IF(OR(F164="",I164=""),"",F164*I164)</f>
+        <v/>
+      </c>
+      <c r="L164" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M164" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N164" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に相談申込完了</t>
+        </is>
+      </c>
+      <c r="O164" s="5" t="inlineStr">
+        <is>
+          <t>不正・不備・重複／18歳未満の申込／学生・無職の方／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P164" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q164" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R164" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S164" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T164" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U164" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V164" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W164" s="5" t="inlineStr">
+        <is>
+          <t>「営業を面白くする」を訴求する営業職特化。確定率28.57%・EPC30.3円</t>
+        </is>
+      </c>
+      <c r="X164" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y164" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z164" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA164" s="5" t="inlineStr">
+        <is>
+          <t>s00000026770001</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>マイキャリ（自己分析の「質」が内定の「納得度」を変える新卒エージェント）</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>アクシス株式会社</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>26〜27卒</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>新規キャリア面談実施</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>キャリア面談実施完了</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="n"/>
+      <c r="J165" s="6" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="K165" s="8">
+        <f>IF(OR(F165="",I165=""),"",F165*I165)</f>
+        <v/>
+      </c>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M165" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N165" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談実施完了</t>
+        </is>
+      </c>
+      <c r="O165" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・入力不備・なりすまし／専門学生除外等の対象外条件／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P165" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q165" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R165" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S165" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T165" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U165" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V165" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W165" s="5" t="inlineStr">
+        <is>
+          <t>自己分析支援を軸にした新卒エージェント。確定率は非表示、EPC39.68円</t>
+        </is>
+      </c>
+      <c r="X165" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率データなし）</t>
+        </is>
+      </c>
+      <c r="Y165" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z165" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA165" s="5" t="inlineStr">
+        <is>
+          <t>s00000026731002</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Agent Kikkake（元人事のプロが専属エージェントとして転職サポート）</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Crown_Cat</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>総合(全職種)</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>20代の求職者</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>新規人材紹介申込（企業の方は10,000円）</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>人材紹介申込完了</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J166" s="6" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="K166" s="8">
+        <f>IF(OR(F166="",I166=""),"",F166*I166)</f>
+        <v/>
+      </c>
+      <c r="L166" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M166" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N166" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の求人応募完了</t>
+        </is>
+      </c>
+      <c r="O166" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・不備／外国籍の方／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P166" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q166" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R166" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S166" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T166" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U166" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V166" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W166" s="5" t="inlineStr">
+        <is>
+          <t>確定率7.9%と低め。元人事担当者が専属エージェントとして対応するのが特徴</t>
+        </is>
+      </c>
+      <c r="X166" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y166" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z166" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA166" s="5" t="inlineStr">
+        <is>
+          <t>s00000026551002</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>経理Jobs（経理特化の転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>株式会社エクセルプロフェッショナル</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>専門職(経理)</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>経理職経験1年以上</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>新規転職支援申込</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>転職支援申込完了</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="n"/>
+      <c r="J167" s="6" t="n"/>
+      <c r="K167" s="8">
+        <f>IF(OR(F167="",I167=""),"",F167*I167)</f>
+        <v/>
+      </c>
+      <c r="L167" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M167" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N167" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより7日以内に経理職経験1年以上の方の申込完了</t>
+        </is>
+      </c>
+      <c r="O167" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・キャンセル・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P167" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q167" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R167" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S167" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T167" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U167" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V167" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W167" s="5" t="inlineStr">
+        <is>
+          <t>経理特化のニッチエージェント。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X167" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y167" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z167" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA167" s="5" t="inlineStr">
+        <is>
+          <t>s00000026359002</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>ホワイトアカデミー（大学生・既卒のホワイト企業就職サポート）</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Avalon_Consulting株式会社</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>新卒・既卒</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>大学生・既卒</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>新規面談成立</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>面談成立</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="n"/>
+      <c r="J168" s="6" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="K168" s="8">
+        <f>IF(OR(F168="",I168=""),"",F168*I168)</f>
+        <v/>
+      </c>
+      <c r="L168" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M168" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより面談成立</t>
+        </is>
+      </c>
+      <c r="O168" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・迷惑行為／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P168" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q168" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R168" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S168" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T168" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U168" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V168" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W168" s="5" t="inlineStr">
+        <is>
+          <t>既存の「ホワイトアカデミー」系列（20代社会人向け・転職成功保証付き）とは別の大学生・既卒向けプログラム。確定率非表示、EPC66.66円</t>
+        </is>
+      </c>
+      <c r="X168" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率データなし）</t>
+        </is>
+      </c>
+      <c r="Y168" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z168" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA168" s="5" t="inlineStr">
+        <is>
+          <t>s00000025580001</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Cic工場求人サイト（派遣のお仕事紹介）</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>株式会社シーアイシー</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>製造業(派遣)</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>求人応募者</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>新規登録（新規登録予約も同額5,000円）</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I169" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J169" s="6" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="K169" s="8">
+        <f>IF(OR(F169="",I169=""),"",F169*I169)</f>
+        <v/>
+      </c>
+      <c r="L169" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M169" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N169" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に登録完了</t>
+        </is>
+      </c>
+      <c r="O169" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・不正・入力不備／LINE経由の申込NG／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P169" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q169" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R169" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S169" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T169" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U169" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V169" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W169" s="5" t="inlineStr">
+        <is>
+          <t>工場派遣特化。確定率25%・EPC32.25円</t>
+        </is>
+      </c>
+      <c r="X169" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y169" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z169" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA169" s="5" t="inlineStr">
+        <is>
+          <t>s00000025487001</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>majicari（有料キャリコーチングと同水準の相談を無料提供）</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>キャリアコーチング</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>40代以下（推定）</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>新規面談実施</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>面談実施完了</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J170" s="6" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="K170" s="8">
+        <f>IF(OR(F170="",I170=""),"",F170*I170)</f>
+        <v/>
+      </c>
+      <c r="L170" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M170" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N170" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談実施完了</t>
+        </is>
+      </c>
+      <c r="O170" s="5" t="inlineStr">
+        <is>
+          <t>同一人物からの重複申込／不正・キャンセル／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P170" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q170" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R170" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S170" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T170" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U170" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V170" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W170" s="5" t="inlineStr">
+        <is>
+          <t>確定率45.45%だがEPC19.09円と低め。無料でキャリアコーチングを提供するのが特徴</t>
+        </is>
+      </c>
+      <c r="X170" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y170" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z170" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA170" s="5" t="inlineStr">
+        <is>
+          <t>s00000021803001</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>アカリクキャリア（院卒・博士向け転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アカリク</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>新卒・研究職(院卒・博士)</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>院卒・博士、社会人経験1年以上</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>新規無料会員登録</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I171" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J171" s="6" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="K171" s="8">
+        <f>IF(OR(F171="",I171=""),"",F171*I171)</f>
+        <v/>
+      </c>
+      <c r="L171" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M171" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N171" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了</t>
+        </is>
+      </c>
+      <c r="O171" s="5" t="inlineStr">
+        <is>
+          <t>外国籍の方の登録／登録情報が不備・本人と異なる場合／メールへの連絡不通／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P171" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q171" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R171" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S171" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T171" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U171" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V171" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W171" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主アカリク系列（就職エージェント・イベント）の社会人向け版。確定率25%・EPC46.55円</t>
+        </is>
+      </c>
+      <c r="X171" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y171" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z171" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA171" s="5" t="inlineStr">
+        <is>
+          <t>s00000023028002</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>ドライバーズワーク（タクシードライバー特化の転職サービス）</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>株式会社カラフル</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>ドライバー・運輸</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>普通自動車免許保有者</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I172" s="7" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="J172" s="6" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="K172" s="8">
+        <f>IF(OR(F172="",I172=""),"",F172*I172)</f>
+        <v/>
+      </c>
+      <c r="L172" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M172" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の登録完了</t>
+        </is>
+      </c>
+      <c r="O172" s="5" t="inlineStr">
+        <is>
+          <t>過去1年以内の重複登録／1世帯2回以上の申込／不正／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P172" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q172" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R172" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S172" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T172" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U172" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V172" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W172" s="5" t="inlineStr">
+        <is>
+          <t>タクシードライバー特化。確定率7.69%・EPC13.08円と低め</t>
+        </is>
+      </c>
+      <c r="X172" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y172" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z172" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA172" s="5" t="inlineStr">
+        <is>
+          <t>s00000024432002</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>BEET-AGENT（経理・財務が評価される企業への転職）</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アシロ</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>専門職(経理・財務)</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>経理・財務職経験者、東京/神奈川/埼玉/千葉在住</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I173" s="7" t="n"/>
+      <c r="J173" s="6" t="n"/>
+      <c r="K173" s="8">
+        <f>IF(OR(F173="",I173=""),"",F173*I173)</f>
+        <v/>
+      </c>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M173" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N173" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内にメールでの本人確認完了</t>
+        </is>
+      </c>
+      <c r="O173" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・なりすまし・悪意／1世帯2回以上の申込／対象エリア・経験年数不足の場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P173" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q173" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R173" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S173" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T173" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U173" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V173" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W173" s="5" t="inlineStr">
+        <is>
+          <t>経理・財務特化でエリア限定（首都圏）。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X173" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y173" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z173" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA173" s="5" t="inlineStr">
+        <is>
+          <t>s00000024873001</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>hape Agent（20代30代の若手営業職特化の転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>株式会社hape</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>営業職(20〜30代)</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>正社員経験者、23〜35歳</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>新規無料転職相談申込</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>無料転職相談申込完了</t>
+        </is>
+      </c>
+      <c r="I174" s="7" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J174" s="6" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="K174" s="8">
+        <f>IF(OR(F174="",I174=""),"",F174*I174)</f>
+        <v/>
+      </c>
+      <c r="L174" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M174" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N174" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に無料転職相談申込完了</t>
+        </is>
+      </c>
+      <c r="O174" s="5" t="inlineStr">
+        <is>
+          <t>キャンセル・虚偽・なりすまし／1世帯2回以上の申込／外国籍の方／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P174" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q174" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R174" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S174" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T174" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U174" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V174" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W174" s="5" t="inlineStr">
+        <is>
+          <t>確定率64.7%・EPC354.33円と営業職特化系の中でも高水準</t>
+        </is>
+      </c>
+      <c r="X174" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y174" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z174" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA174" s="5" t="inlineStr">
+        <is>
+          <t>s00000025290001</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>atGPジョブトレ（障害別就労移行支援、6コース展開）</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ゼネラルパートナーズ</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>障害者向け(就労移行支援)</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>発達障害・統合失調症・うつ症状・難病・聴覚障害等、コースごとに対象障害種別が異なる</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>新規登録（コース共通）</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>コース登録完了</t>
+        </is>
+      </c>
+      <c r="I175" s="7" t="n">
+        <v>0.4705</v>
+      </c>
+      <c r="J175" s="6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="K175" s="8">
+        <f>IF(OR(F175="",I175=""),"",F175*I175)</f>
+        <v/>
+      </c>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M175" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N175" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談等実施完了（コースにより詳細条件が異なる）</t>
+        </is>
+      </c>
+      <c r="O175" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・不正・重複／メールや電話等で連絡がつかない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P175" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q175" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R175" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S175" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T175" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U175" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V175" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W175" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主・同一報酬体系のコース違い6プログラムを1行に集約（一覧: 確定率47.05%/EPC12.25円、個別コースは確定率・EPC非表示が多い）。就労移行支援利用率91%を訴求</t>
+        </is>
+      </c>
+      <c r="X175" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、6コース分をまとめて記載）</t>
+        </is>
+      </c>
+      <c r="Y175" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z175" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA175" s="5" t="inlineStr">
+        <is>
+          <t>s00000017969007 / s00000017969008 / s00000017969006 / s00000017969004 / s00000017969003 / s00000017969002</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>保育士メトロ（保育士の転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ワシントン</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者、20〜30代女性</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I176" s="7" t="n"/>
+      <c r="J176" s="6" t="n"/>
+      <c r="K176" s="8">
+        <f>IF(OR(F176="",I176=""),"",F176*I176)</f>
+        <v/>
+      </c>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M176" s="5" t="inlineStr">
+        <is>
+          <t>約15日</t>
+        </is>
+      </c>
+      <c r="N176" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより14日以内に電話等で本人確認完了</t>
+        </is>
+      </c>
+      <c r="O176" s="5" t="inlineStr">
+        <is>
+          <t>イタズラや冷やかしと思われる場合／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P176" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q176" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R176" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S176" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T176" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U176" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V176" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W176" s="5" t="inlineStr">
+        <is>
+          <t>都市部（メトロ沿線）に特化した保育士転職支援。確定率・EPCとも非表示、確定目安約15日</t>
+        </is>
+      </c>
+      <c r="X176" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y176" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z176" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA176" s="5" t="inlineStr">
+        <is>
+          <t>s00000014574006</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>エンジニアファクトリー（ITフリーランス向け高額×優良案件紹介）</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アイドマ・ホールディングス</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>IT(フリーランスエンジニア)</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>20〜50代のフリーランスエンジニア</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="n"/>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>勤務地により異なる（関東13,000円／関西等15,000円）</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I177" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="6" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="K177" s="8">
+        <f>IF(OR(F177="",I177=""),"",F177*I177)</f>
+        <v/>
+      </c>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M177" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了、面談実施等</t>
+        </is>
+      </c>
+      <c r="O177" s="5" t="inlineStr">
+        <is>
+          <t>入力不備／重複登録／不正な申込／55歳以上の場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P177" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q177" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R177" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S177" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T177" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U177" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V177" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W177" s="5" t="inlineStr">
+        <is>
+          <t>確定率100%表示・平均年収810万円を訴求。報酬が勤務地により2値ある点に注意</t>
+        </is>
+      </c>
+      <c r="X177" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、報酬は勤務地区分により複数あり単一値なし）</t>
+        </is>
+      </c>
+      <c r="Y177" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z177" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA177" s="5" t="inlineStr">
+        <is>
+          <t>s00000016458004</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>FoodsLabo（飲食業界特化の転職支援サービス・クオレガエージェント）</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>株式会社クオレガ</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>飲食業界</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>飲食業界経験者、50代以下</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I178" s="7" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="J178" s="6" t="n">
+        <v>321.13</v>
+      </c>
+      <c r="K178" s="8">
+        <f>IF(OR(F178="",I178=""),"",F178*I178)</f>
+        <v/>
+      </c>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M178" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N178" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより14日以内のエントリー</t>
+        </is>
+      </c>
+      <c r="O178" s="5" t="inlineStr">
+        <is>
+          <t>明らかに就活意思がないと判断された場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P178" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q178" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R178" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S178" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T178" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U178" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V178" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W178" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主の別プログラム（既存行、報酬7,000円版）とは異なるID・報酬体系。確定率21.96%・EPC321.13円</t>
+        </is>
+      </c>
+      <c r="X178" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y178" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z178" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA178" s="5" t="inlineStr">
+        <is>
+          <t>s00000017827001</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>保育バランス（保育士のための転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>株式会社サウンド</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者、20〜50代女性</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I179" s="7" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="J179" s="6" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="K179" s="8">
+        <f>IF(OR(F179="",I179=""),"",F179*I179)</f>
+        <v/>
+      </c>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M179" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N179" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより14日以内に電話連絡が取れること</t>
+        </is>
+      </c>
+      <c r="O179" s="5" t="inlineStr">
+        <is>
+          <t>14日以内に電話連絡がとれない場合／イタズラ利用がある場合／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P179" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q179" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R179" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S179" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T179" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U179" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V179" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W179" s="5" t="inlineStr">
+        <is>
+          <t>確定率66.66%・EPC31.44円。同ジャンルの保育士メトロ・保育Aidと系列比較可能</t>
+        </is>
+      </c>
+      <c r="X179" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y179" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z179" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA179" s="5" t="inlineStr">
+        <is>
+          <t>s00000014574002</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>はいく畑（保育専門求人サイト）</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>新規サービス登録</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>サービス登録完了</t>
+        </is>
+      </c>
+      <c r="I180" s="7" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="J180" s="6" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="K180" s="8">
+        <f>IF(OR(F180="",I180=""),"",F180*I180)</f>
+        <v/>
+      </c>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M180" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N180" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の本人確認完了</t>
+        </is>
+      </c>
+      <c r="O180" s="5" t="inlineStr">
+        <is>
+          <t>虚偽登録・重複・不正／電話番号記載なし／対象外エリアの場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P180" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q180" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R180" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S180" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T180" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U180" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V180" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W180" s="5" t="inlineStr">
+        <is>
+          <t>関東・関西・東海の保育士人材情報3,000件以上を訴求。確定率17.39%・EPC20.48円</t>
+        </is>
+      </c>
+      <c r="X180" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y180" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z180" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA180" s="5" t="inlineStr">
+        <is>
+          <t>s00000008824003</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>MC介護のお仕事（メディカル・コンシェルジュ求人サイト）</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>株式会社エス・エム・エス</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>医療・介護</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>介護資格保有者</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>会員登録</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="J181" s="6" t="n">
+        <v>51.18</v>
+      </c>
+      <c r="K181" s="8">
+        <f>IF(OR(F181="",I181=""),"",F181*I181)</f>
+        <v/>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M181" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>介護士等資格保有者からの登録、1週間以内にメールまたは電話での本人確認完了</t>
+        </is>
+      </c>
+      <c r="O181" s="5" t="inlineStr">
+        <is>
+          <t>同一人物からの重複登録／申込フォームからの重複登録／不正な申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P181" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q181" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R181" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S181" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T181" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U181" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V181" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W181" s="5" t="inlineStr">
+        <is>
+          <t>確定率2.12%と極端に低いがEPC51.18円。同一広告主エス・エム・エスの他プログラム（ナース専科・国試黒本等）と系列</t>
+        </is>
+      </c>
+      <c r="X181" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y181" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z181" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA181" s="5" t="inlineStr">
+        <is>
+          <t>s00000011449004</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>レバテッククリエイター（フリーランス向けWeb・ゲームクリエイター案件情報）</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>レバレジーズ株式会社</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>IT(フリーランスクリエイター)</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>フリーランスWeb・ゲームクリエイター</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I182" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J182" s="6" t="n">
+        <v>294.39</v>
+      </c>
+      <c r="K182" s="8">
+        <f>IF(OR(F182="",I182=""),"",F182*I182)</f>
+        <v/>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M182" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了</t>
+        </is>
+      </c>
+      <c r="O182" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P182" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q182" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R182" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S182" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T182" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U182" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V182" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W182" s="5" t="inlineStr">
+        <is>
+          <t>確定率20%だがEPC294.39円と高水準。同一広告主レバレジーズのフリーランス系（Midworks等）と系列</t>
+        </is>
+      </c>
+      <c r="X182" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y182" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z182" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA182" s="5" t="inlineStr">
+        <is>
+          <t>s00000011866023</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>介護JJ（介護職専門の転職サイト、介護応援プロジェクト実施中）</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ハートフルケア</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>医療・介護</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>介護資格保有者・実務経験者</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="6" t="n"/>
+      <c r="K183" s="8">
+        <f>IF(OR(F183="",I183=""),"",F183*I183)</f>
+        <v/>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M183" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O183" s="5" t="inlineStr">
+        <is>
+          <t>上記応募が既に他の転職サイトを通じている場合／二重応募・重複登録／日本国外からの登録／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P183" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q183" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R183" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S183" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T183" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U183" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V183" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W183" s="5" t="inlineStr">
+        <is>
+          <t>20〜40代の中高年層がメインターゲット。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X183" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y183" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z183" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA183" s="5" t="inlineStr">
+        <is>
+          <t>s00000013807005</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>保育Aid（保育士さんのための転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>株式会社クイック</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者、20〜50代女性</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I184" s="7" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="J184" s="6" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="K184" s="8">
+        <f>IF(OR(F184="",I184=""),"",F184*I184)</f>
+        <v/>
+      </c>
+      <c r="L184" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M184" s="5" t="inlineStr">
+        <is>
+          <t>約15日</t>
+        </is>
+      </c>
+      <c r="N184" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了、14日以内に電話連絡が取れること</t>
+        </is>
+      </c>
+      <c r="O184" s="5" t="inlineStr">
+        <is>
+          <t>14日以内に電話連絡がとれない場合／イタズラ利用／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P184" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q184" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R184" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S184" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T184" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U184" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V184" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W184" s="5" t="inlineStr">
+        <is>
+          <t>同ジャンルの保育士メトロ・保育バランスと系列比較可能。確定率11.11%・EPC16.69円</t>
+        </is>
+      </c>
+      <c r="X184" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y184" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z184" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA184" s="5" t="inlineStr">
+        <is>
+          <t>s00000014574001</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>LIFULL HOME'S（不動産業界の転職専門支援サービス）</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>株式会社LIFULL</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>不動産業界</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>関東・関西・九州の対象エリア在住、不動産業界経験者</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>新規カウンセリング</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>カウンセリング完了</t>
+        </is>
+      </c>
+      <c r="I185" s="7" t="n">
+        <v>0.8888</v>
+      </c>
+      <c r="J185" s="6" t="n">
+        <v>248.36</v>
+      </c>
+      <c r="K185" s="8">
+        <f>IF(OR(F185="",I185=""),"",F185*I185)</f>
+        <v/>
+      </c>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M185" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内にカウンセリング実施完了</t>
+        </is>
+      </c>
+      <c r="O185" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・いたずら／キャンセル（辞退／連絡不通等）／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P185" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q185" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R185" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S185" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T185" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U185" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V185" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W185" s="5" t="inlineStr">
+        <is>
+          <t>確定率88.88%・EPC248.36円と高水準。不動産大手LIFULLグループの転職支援</t>
+        </is>
+      </c>
+      <c r="X185" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y185" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z185" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA185" s="5" t="inlineStr">
+        <is>
+          <t>s00000008688004</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>保育士人材バンク（保育士の「熱転」転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>株式会社エス・エム・エス</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I186" s="7" t="n">
+        <v>0.8683999999999999</v>
+      </c>
+      <c r="J186" s="6" t="n">
+        <v>6381.31</v>
+      </c>
+      <c r="K186" s="8">
+        <f>IF(OR(F186="",I186=""),"",F186*I186)</f>
+        <v/>
+      </c>
+      <c r="L186" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M186" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N186" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了</t>
+        </is>
+      </c>
+      <c r="O186" s="5" t="inlineStr">
+        <is>
+          <t>重複・入力不備・不備・虚偽等サービス対象外／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P186" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q186" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R186" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S186" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T186" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U186" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V186" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W186" s="5" t="inlineStr">
+        <is>
+          <t>確定率86.84%・EPC6,381.31円と全案件中でも最高水準級。同一広告主エス・エム・エスの主力保育士サービス</t>
+        </is>
+      </c>
+      <c r="X186" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y186" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z186" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA186" s="5" t="inlineStr">
+        <is>
+          <t>s00000012498025</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>工場求人フォルダ（工場・製造派遣、寮完備の全国対応）</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>株式会社マニュファクチュアリングサービス</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>製造業(派遣)</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>18〜59歳男女、北海道・沖縄を除く全国対応</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>新規求人応募（キャンペーン中、通常5,500円、2026/08/27〜09/30）</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>求人応募完了</t>
+        </is>
+      </c>
+      <c r="I187" s="7" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="J187" s="6" t="n"/>
+      <c r="K187" s="8">
+        <f>IF(OR(F187="",I187=""),"",F187*I187)</f>
+        <v/>
+      </c>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M187" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N187" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の応募完了</t>
+        </is>
+      </c>
+      <c r="O187" s="5" t="inlineStr">
+        <is>
+          <t>北海道・沖縄からの応募／連絡先不備／重複登録／不正／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P187" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q187" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R187" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S187" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T187" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U187" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V187" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W187" s="5" t="inlineStr">
+        <is>
+          <t>寮完備の工場派遣。確定率29.41%、EPCは非表示。キャンペーン期限に要注意</t>
+        </is>
+      </c>
+      <c r="X187" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y187" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z187" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA187" s="5" t="inlineStr">
+        <is>
+          <t>s00000027272001</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>レバウェル保育士（保育士の求人・転職・募集）</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>レバレジーズ株式会社</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>医療・保育(保育士)</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>保育士資格保有者</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="n">
+        <v>0.9217</v>
+      </c>
+      <c r="J188" s="6" t="n">
+        <v>1327.96</v>
+      </c>
+      <c r="K188" s="8">
+        <f>IF(OR(F188="",I188=""),"",F188*I188)</f>
+        <v/>
+      </c>
+      <c r="L188" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M188" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N188" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O188" s="5" t="inlineStr">
+        <is>
+          <t>サービス利用意思のない登録／虚偽・重複・入力不備等／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P188" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q188" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R188" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S188" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T188" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U188" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V188" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W188" s="5" t="inlineStr">
+        <is>
+          <t>確定率92.17%・EPC1,327.96円と保育士系の中でも最高水準。同一広告主レバレジーズの保育士特化版</t>
+        </is>
+      </c>
+      <c r="X188" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y188" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z188" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA188" s="5" t="inlineStr">
+        <is>
+          <t>s00000011866026</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>キャリアパーク就職エージェント（既卒・第二新卒版）</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>ポート株式会社</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>既卒・第二新卒</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>既卒・第二新卒</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="n">
+        <v>6436</v>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>新規エントリー</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>エントリー完了</t>
+        </is>
+      </c>
+      <c r="I189" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J189" s="6" t="n">
+        <v>112.14</v>
+      </c>
+      <c r="K189" s="8">
+        <f>IF(OR(F189="",I189=""),"",F189*I189)</f>
+        <v/>
+      </c>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M189" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のエージェントサービス利用完了</t>
+        </is>
+      </c>
+      <c r="O189" s="5" t="inlineStr">
+        <is>
+          <t>サービス利用意思がないと判断される場合／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P189" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q189" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R189" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S189" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T189" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U189" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V189" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W189" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主の既存行（新卒版・報酬4,000円）とは対象・報酬が異なる既卒/第二新卒版。確定率75%・EPC112.14円</t>
+        </is>
+      </c>
+      <c r="X189" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y189" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z189" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA189" s="5" t="inlineStr">
+        <is>
+          <t>s00000018455004</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>宅魔Jobエージェント（不動産業界専門の転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>株式会社リアルエステートWORKS</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>不動産業界</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>43歳以下、正社員経験者</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="n">
+        <v>5635</v>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>登録完了</t>
+        </is>
+      </c>
+      <c r="I190" s="7" t="n">
+        <v>0.4769</v>
+      </c>
+      <c r="J190" s="6" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="K190" s="8">
+        <f>IF(OR(F190="",I190=""),"",F190*I190)</f>
+        <v/>
+      </c>
+      <c r="L190" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M190" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N190" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に登録完了</t>
+        </is>
+      </c>
+      <c r="O190" s="5" t="inlineStr">
+        <is>
+          <t>情報不備・重複・キャンセル／パパ活・スカウトからの申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P190" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q190" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R190" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S190" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T190" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U190" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V190" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W190" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のリアルエステートWORKS（既存行）と系列。確定率47.69%・EPC15.54円</t>
+        </is>
+      </c>
+      <c r="X190" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y190" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z190" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA190" s="5" t="inlineStr">
+        <is>
+          <t>s00000021009002</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>パーソルイノベーション転職エージェント（配送ドライバー特化）</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>パーソルイノベーション株式会社</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>ドライバー・運輸</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>18〜49歳</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="J191" s="6" t="n">
+        <v>171.61</v>
+      </c>
+      <c r="K191" s="8">
+        <f>IF(OR(F191="",I191=""),"",F191*I191)</f>
+        <v/>
+      </c>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M191" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N191" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより会員登録完了</t>
+        </is>
+      </c>
+      <c r="O191" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・いたずら・重複成果・キャンセル・不正／電話不通／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P191" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q191" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R191" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S191" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T191" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U191" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V191" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W191" s="5" t="inlineStr">
+        <is>
+          <t>確定率82.35%・EPC171.61円と高水準。同一広告主のみつけあ（既存行、介護特化）と系列</t>
+        </is>
+      </c>
+      <c r="X191" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y191" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z191" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA191" s="5" t="inlineStr">
+        <is>
+          <t>s00000026823002</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>スタクラ（スタートアップ転職なら）</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>株式会社スタートアップクラス</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>スタートアップ</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>マーケ・営業・SaaS・PMO・CFO・COO等</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="n"/>
+      <c r="J192" s="6" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="K192" s="8">
+        <f>IF(OR(F192="",I192=""),"",F192*I192)</f>
+        <v/>
+      </c>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M192" s="5" t="inlineStr">
+        <is>
+          <t>約45日</t>
+        </is>
+      </c>
+      <c r="N192" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の登録完了</t>
+        </is>
+      </c>
+      <c r="O192" s="5" t="inlineStr">
+        <is>
+          <t>不正・虚偽・いたずら／ログイン不可のASPストラクチャ不可／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P192" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q192" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R192" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S192" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T192" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U192" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V192" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W192" s="5" t="inlineStr">
+        <is>
+          <t>スタートアップ専門求人サイト日本最大級を訴求。確定率64.28%表示だがEPCは非表示（数値の混同に注意）</t>
+        </is>
+      </c>
+      <c r="X192" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPC非表示のためこの値は確定率）</t>
+        </is>
+      </c>
+      <c r="Y192" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z192" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA192" s="5" t="inlineStr">
+        <is>
+          <t>s00000026900001</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>MyStar（補助金活用で在宅ワークへのキャリアチェンジを完全サポート）</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ハウマッチ</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>在宅ワーク・リスキリング</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>女性メイン、在宅ワーク志望</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>新規無料相談参加</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>無料相談参加完了</t>
+        </is>
+      </c>
+      <c r="I193" s="7" t="n">
+        <v>0.7141999999999999</v>
+      </c>
+      <c r="J193" s="6" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="K193" s="8">
+        <f>IF(OR(F193="",I193=""),"",F193*I193)</f>
+        <v/>
+      </c>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M193" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N193" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の無料相談参加完了</t>
+        </is>
+      </c>
+      <c r="O193" s="5" t="inlineStr">
+        <is>
+          <t>不正・入力不備・いたずら／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P193" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q193" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R193" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S193" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T193" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U193" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V193" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W193" s="5" t="inlineStr">
+        <is>
+          <t>Webデザイン等のリスキリング＋転職支援。確定率71.42%・EPC52.36円</t>
+        </is>
+      </c>
+      <c r="X193" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y193" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z193" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA193" s="5" t="inlineStr">
+        <is>
+          <t>s00000027421001</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>TRIPLE THREE（外食産業に新基準！人財領域で一気通貫サポート）</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>株式会社トリプルスリー</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>飲食業界(法人向け含む)</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>飲食・小売等外食産業</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>新規問い合わせ</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>問い合わせ完了</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="n"/>
+      <c r="J194" s="6" t="n"/>
+      <c r="K194" s="8">
+        <f>IF(OR(F194="",I194=""),"",F194*I194)</f>
+        <v/>
+      </c>
+      <c r="L194" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M194" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N194" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に問い合わせ完了</t>
+        </is>
+      </c>
+      <c r="O194" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・入力不備／電話番号・メールアドレス不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P194" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q194" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R194" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S194" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T194" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U194" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V194" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W194" s="5" t="inlineStr">
+        <is>
+          <t>採用側（企業）向けサービスの側面もあるため対象の確認が必要。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X194" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y194" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z194" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA194" s="5" t="inlineStr">
+        <is>
+          <t>s00000026763003</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>dodaチャレンジ（障害者の就職・転職）</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>パーソルダイバース株式会社</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>障害者向け</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>60歳未満、障害者手帳保有者</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>新規面談</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>キャリアカウンセリング面談完了</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="J195" s="6" t="n">
+        <v>206.02</v>
+      </c>
+      <c r="K195" s="8">
+        <f>IF(OR(F195="",I195=""),"",F195*I195)</f>
+        <v/>
+      </c>
+      <c r="L195" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M195" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N195" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEB申込、30日以内のキャリアカウンセリング面談完了</t>
+        </is>
+      </c>
+      <c r="O195" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・悪意・入力不備／服薬状況の連絡不通／サービス利用意思不明／リスティング違反／1世帯2回以上</t>
+        </is>
+      </c>
+      <c r="P195" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q195" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R195" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S195" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T195" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U195" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V195" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W195" s="5" t="inlineStr">
+        <is>
+          <t>dodaブランドの障害者転職支援サービス。確定率17.66%・EPC206.02円</t>
+        </is>
+      </c>
+      <c r="X195" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y195" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z195" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA195" s="5" t="inlineStr">
+        <is>
+          <t>s00000019630001</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>TECH-BASE就活エージェント（IT業界志望学生の新卒紹介サービス）</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>シンクトワイス株式会社</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>新卒・IT(未経験)</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>27卒、日本国籍学生</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="n"/>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>ステップ制（新規面談予約15,000円／新規面談完了7,000円）</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>面談予約完了または面談完了</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" s="6" t="n"/>
+      <c r="K196" s="8">
+        <f>IF(OR(F196="",I196=""),"",F196*I196)</f>
+        <v/>
+      </c>
+      <c r="L196" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M196" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N196" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に面談予約または面談完了</t>
+        </is>
+      </c>
+      <c r="O196" s="5" t="inlineStr">
+        <is>
+          <t>既卒・大学院生の対象外条件あり／虚偽・重複・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P196" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q196" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R196" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S196" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T196" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U196" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V196" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W196" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主シンクトワイス系列（TECH::BASE・キャリセン就活エージェント）のIT特化版。確定率100%表示だが報酬が2段階でEPCは非表示</t>
+        </is>
+      </c>
+      <c r="X196" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、報酬は段階制のため単一値なし、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y196" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z196" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA196" s="5" t="inlineStr">
+        <is>
+          <t>s00000022228004</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>DiG UP CAREER（利用満足度90%！支援の手厚い就活エージェント）</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>ロイド株式会社</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>大学3〜4年生、就職希望者</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>新規オンライン面談</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>オンライン面談完了</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J197" s="6" t="n"/>
+      <c r="K197" s="8">
+        <f>IF(OR(F197="",I197=""),"",F197*I197)</f>
+        <v/>
+      </c>
+      <c r="L197" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M197" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N197" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のオンライン面談完了</t>
+        </is>
+      </c>
+      <c r="O197" s="5" t="inlineStr">
+        <is>
+          <t>外国籍の方／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P197" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q197" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R197" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S197" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T197" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U197" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V197" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W197" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のゼロイチ転職（既存行、第二新卒版）の新卒学生向け版。確定率25%、EPCは非表示</t>
+        </is>
+      </c>
+      <c r="X197" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y197" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z197" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA197" s="5" t="inlineStr">
+        <is>
+          <t>s00000023866003</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>歯科衛生士転職ナビ（歯科衛生士の求人最大級）</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>PECORI株式会社</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>医療(歯科衛生士)</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>歯科衛生士有資格者</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>新規電話面談</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>電話面談完了</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="J198" s="6" t="n">
+        <v>151.89</v>
+      </c>
+      <c r="K198" s="8">
+        <f>IF(OR(F198="",I198=""),"",F198*I198)</f>
+        <v/>
+      </c>
+      <c r="L198" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N198" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録後14日以内に電話面談を実施完了</t>
+        </is>
+      </c>
+      <c r="O198" s="5" t="inlineStr">
+        <is>
+          <t>悪戯・虚偽・不正・キャンセル・重複・入力不備／1世帯2回以上／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P198" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q198" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R198" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S198" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T198" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U198" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V198" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W198" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主PECORI系列（ケアマネ・歯科医師専門）の歯科衛生士版。確定率64.1%・EPC151.89円と系列内でも高水準</t>
+        </is>
+      </c>
+      <c r="X198" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y198" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z198" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA198" s="5" t="inlineStr">
+        <is>
+          <t>s00000024076001</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>タネックス（10代20代向け正社員転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ミライス</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>未経験・一般(10〜20代)</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>10〜20代、正社員経験不問</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I199" s="7" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="J199" s="6" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K199" s="8">
+        <f>IF(OR(F199="",I199=""),"",F199*I199)</f>
+        <v/>
+      </c>
+      <c r="L199" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M199" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N199" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより登録完了</t>
+        </is>
+      </c>
+      <c r="O199" s="5" t="inlineStr">
+        <is>
+          <t>過去の重複登録／不正／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P199" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q199" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R199" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S199" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T199" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U199" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V199" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W199" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のドライバーズワーク（既存行）と系列。確定率3.7%と低め、EPC21.43円</t>
+        </is>
+      </c>
+      <c r="X199" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y199" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z199" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA199" s="5" t="inlineStr">
+        <is>
+          <t>s00000024432001</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>かいご畑（介護専門求人サイト、人材サービス登録）</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ニッソーネット</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>医療・介護</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>介護資格保有者</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>新規人材サービス登録</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>人材サービス登録完了</t>
+        </is>
+      </c>
+      <c r="I200" s="7" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="J200" s="6" t="n">
+        <v>135.61</v>
+      </c>
+      <c r="K200" s="8">
+        <f>IF(OR(F200="",I200=""),"",F200*I200)</f>
+        <v/>
+      </c>
+      <c r="L200" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M200" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N200" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEB問合せ後、30日以内の登録完了</t>
+        </is>
+      </c>
+      <c r="O200" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・いたずら・代理登録・現在就業中／同業者からの申込／2週間以内のアクションがない場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P200" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q200" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R200" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S200" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T200" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U200" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V200" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W200" s="5" t="inlineStr">
+        <is>
+          <t>介護専門求人サイト最大手級。0円で介護資格取得支援を訴求。確定率40.46%・EPC135.61円</t>
+        </is>
+      </c>
+      <c r="X200" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y200" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z200" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA200" s="5" t="inlineStr">
+        <is>
+          <t>s00000008824002</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>レバウェル介護（介護業界特化の転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>レバレジーズ株式会社</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>医療・介護</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>介護資格保有者</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="n"/>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録（金額表記不鮮明、要再確認）</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I201" s="7" t="n">
+        <v>0.7917</v>
+      </c>
+      <c r="J201" s="6" t="n">
+        <v>732.17</v>
+      </c>
+      <c r="K201" s="8">
+        <f>IF(OR(F201="",I201=""),"",F201*I201)</f>
+        <v/>
+      </c>
+      <c r="L201" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M201" s="5" t="inlineStr">
+        <is>
+          <t>約60日</t>
+        </is>
+      </c>
+      <c r="N201" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／過去に当サービスを利用したことがない方</t>
+        </is>
+      </c>
+      <c r="O201" s="5" t="inlineStr">
+        <is>
+          <t>サービス利用意思のない登録／虚偽・重複・入力不備等／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P201" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q201" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R201" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S201" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T201" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U201" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V201" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W201" s="5" t="inlineStr">
+        <is>
+          <t>確定率79.17%・EPC732.17円と高水準。同一広告主レバレジーズの介護特化版。報酬額は画像判読不鮮明のため要再確認</t>
+        </is>
+      </c>
+      <c r="X201" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、報酬額要再確認）</t>
+        </is>
+      </c>
+      <c r="Y201" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z201" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA201" s="5" t="inlineStr">
+        <is>
+          <t>s00000022039002</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>POSIWILLエージェント紹介（信頼できる1人に出会える、納得転職）</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>ポジウィル株式会社</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>総合(正社員経験者)</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>20代〜30代、正社員経験者（フリーランス・アルバイト・パート等除く）</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>新規無料相談実施</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>無料相談実施完了</t>
+        </is>
+      </c>
+      <c r="I202" s="7" t="n"/>
+      <c r="J202" s="6" t="n"/>
+      <c r="K202" s="8">
+        <f>IF(OR(F202="",I202=""),"",F202*I202)</f>
+        <v/>
+      </c>
+      <c r="L202" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M202" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N202" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の無料相談実施完了</t>
+        </is>
+      </c>
+      <c r="O202" s="5" t="inlineStr">
+        <is>
+          <t>いたずら・重複／正社員経験のない方の申込／フリーランス・アルバイト等からの申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P202" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q202" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R202" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S202" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T202" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U202" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V202" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W202" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のPOSIWILL CAREER（既存行、コーチング）とは異なるエージェント紹介型サービス。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X202" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y202" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z202" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA202" s="5" t="inlineStr">
+        <is>
+          <t>s00000025557003</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>マーキャリNEXT CAREER（SaaS業界特化の転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>株式会社エニッシュ</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>専門職(SaaS業界)</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>1年以上のSaaS業界営業経験者</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>新規面談</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>面談完了</t>
+        </is>
+      </c>
+      <c r="I203" s="7" t="n">
+        <v>0.4727</v>
+      </c>
+      <c r="J203" s="6" t="n">
+        <v>67.28</v>
+      </c>
+      <c r="K203" s="8">
+        <f>IF(OR(F203="",I203=""),"",F203*I203)</f>
+        <v/>
+      </c>
+      <c r="L203" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M203" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N203" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に面談完了</t>
+        </is>
+      </c>
+      <c r="O203" s="5" t="inlineStr">
+        <is>
+          <t>過去1年以上の利用歴あり／不正・不備・重複／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P203" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q203" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R203" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S203" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T203" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U203" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V203" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W203" s="5" t="inlineStr">
+        <is>
+          <t>SaaS業界特化のニッチ案件。確定率47.27%・EPC67.28円</t>
+        </is>
+      </c>
+      <c r="X203" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y203" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z203" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA203" s="5" t="inlineStr">
+        <is>
+          <t>s00000022372001</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>上京就活（逆転就活実績No.1、マンツーマン就活支援）</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>LDC株式会社</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>新卒</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>大学生等（主に27卒学年、上京希望者）</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>新規無料就活相談参加</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>無料就活相談参加完了</t>
+        </is>
+      </c>
+      <c r="I204" s="7" t="n"/>
+      <c r="J204" s="6" t="n"/>
+      <c r="K204" s="8">
+        <f>IF(OR(F204="",I204=""),"",F204*I204)</f>
+        <v/>
+      </c>
+      <c r="L204" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M204" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N204" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内に相談参加完了</t>
+        </is>
+      </c>
+      <c r="O204" s="5" t="inlineStr">
+        <is>
+          <t>1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P204" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q204" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R204" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S204" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T204" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U204" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V204" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W204" s="5" t="inlineStr">
+        <is>
+          <t>地方学生の上京就活支援に特化。Googleクチコミ評価業界No.1を訴求。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X204" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y204" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z204" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA204" s="5" t="inlineStr">
+        <is>
+          <t>s00000026944001</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>ASSIGN AGENT（若手ハイエンド特化の転職エージェント）</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アサイン</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>ハイクラス(若手)</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>23〜35歳</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="n">
+        <v>7875</v>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>新規キャリア面談完了</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>キャリア面談完了</t>
+        </is>
+      </c>
+      <c r="I205" s="7" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="K205" s="8">
+        <f>IF(OR(F205="",I205=""),"",F205*I205)</f>
+        <v/>
+      </c>
+      <c r="L205" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M205" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N205" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内のキャリア面談完了</t>
+        </is>
+      </c>
+      <c r="O205" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・重複・キャンセル／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P205" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q205" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R205" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S205" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T205" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U205" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V205" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W205" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のASSIGN（既存行、会員登録版）とは別のキャリア面談完了型プログラム。確定率85.71%・EPC110.05円</t>
+        </is>
+      </c>
+      <c r="X205" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y205" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z205" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA205" s="5" t="inlineStr">
+        <is>
+          <t>s00000019900002</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>BEET-AGENT（法務部特化型の転職・求人情報）</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>株式会社アシロ</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>専門職(法務)</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>法務職経験者、東京/神奈川/埼玉/千葉在住</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I206" s="7" t="n"/>
+      <c r="J206" s="6" t="n"/>
+      <c r="K206" s="8">
+        <f>IF(OR(F206="",I206=""),"",F206*I206)</f>
+        <v/>
+      </c>
+      <c r="L206" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M206" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N206" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内にメールでの本人確認完了</t>
+        </is>
+      </c>
+      <c r="O206" s="5" t="inlineStr">
+        <is>
+          <t>虚偽・なりすまし・悪意／1世帯2回以上の申込／対象エリア外の場合／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P206" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q206" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R206" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S206" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T206" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U206" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V206" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W206" s="5" t="inlineStr">
+        <is>
+          <t>同一広告主のBEET-AGENT（既存行、経理財務特化版）とは別の法務部特化版。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X206" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y206" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z206" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA206" s="5" t="inlineStr">
+        <is>
+          <t>s00000024873002</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>エンジニアキャリップ（IT・Web業界を目指せる転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>IT(未経験可)</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>20〜29歳</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>新規会員登録</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>会員登録完了</t>
+        </is>
+      </c>
+      <c r="I207" s="7" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="J207" s="6" t="n">
+        <v>283.37</v>
+      </c>
+      <c r="K207" s="8">
+        <f>IF(OR(F207="",I207=""),"",F207*I207)</f>
+        <v/>
+      </c>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M207" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N207" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の登録完了</t>
+        </is>
+      </c>
+      <c r="O207" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P207" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q207" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R207" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S207" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T207" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U207" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V207" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W207" s="5" t="inlineStr">
+        <is>
+          <t>確定率66.82%・EPC283.37円と高水準。IT未経験のキャリアチェンジ層向け</t>
+        </is>
+      </c>
+      <c r="X207" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y207" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z207" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA207" s="5" t="inlineStr">
+        <is>
+          <t>s00000025727001</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>出会えるエージェント診断（診断で見つける、ぴったりの転職エージェント診断）</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>株式会社iNova</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>総合(診断型マッチング)</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>20〜30代</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>新規面談予約</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>面談予約完了</t>
+        </is>
+      </c>
+      <c r="I208" s="7" t="n"/>
+      <c r="J208" s="6" t="n"/>
+      <c r="K208" s="8">
+        <f>IF(OR(F208="",I208=""),"",F208*I208)</f>
+        <v/>
+      </c>
+      <c r="L208" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M208" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N208" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより30日以内の面談予約完了</t>
+        </is>
+      </c>
+      <c r="O208" s="5" t="inlineStr">
+        <is>
+          <t>キャンセル・不正・申込不備・いたずら／連絡がつかない場合／LINE誘導からの重複申込等／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P208" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q208" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R208" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S208" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T208" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U208" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V208" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W208" s="5" t="inlineStr">
+        <is>
+          <t>「診断」形式で1000人以上のエージェントから紹介するマッチングサービス。確定率・EPCとも非表示</t>
+        </is>
+      </c>
+      <c r="X208" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力、確定率・EPCデータなし）</t>
+        </is>
+      </c>
+      <c r="Y208" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z208" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA208" s="5" t="inlineStr">
+        <is>
+          <t>s00000027541002</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>転職AGENT Navi（完全無料で転職のプロとパーソナルマッチング）</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>circus株式会社</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>総合(マッチング型)</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>20代</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>新規無料相談登録</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>無料相談登録完了</t>
+        </is>
+      </c>
+      <c r="I209" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J209" s="6" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="K209" s="8">
+        <f>IF(OR(F209="",I209=""),"",F209*I209)</f>
+        <v/>
+      </c>
+      <c r="L209" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M209" s="5" t="inlineStr">
+        <is>
+          <t>約30日</t>
+        </is>
+      </c>
+      <c r="N209" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより14日以内にメールまたは電話での本人確認完了</t>
+        </is>
+      </c>
+      <c r="O209" s="5" t="inlineStr">
+        <is>
+          <t>重複・虚偽・キャンセル／1世帯2回以上の申込／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P209" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q209" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R209" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S209" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T209" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U209" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V209" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W209" s="5" t="inlineStr">
+        <is>
+          <t>300人以上のキャリアエージェントからマッチングするサービス。確定率75%だがEPC13.17円と低め</t>
+        </is>
+      </c>
+      <c r="X209" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y209" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z209" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA209" s="5" t="inlineStr">
+        <is>
+          <t>s00000024824001</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>Backup Carrer（バックオフィス業界特化のオンライン転職支援サービス）</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>Mirise_up株式会社</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>専門職(バックオフィス・事務)</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>主に20代女性、40代までの事務系希望者</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>新規面談実施</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>面談実施完了</t>
+        </is>
+      </c>
+      <c r="I210" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J210" s="6" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="K210" s="8">
+        <f>IF(OR(F210="",I210=""),"",F210*I210)</f>
+        <v/>
+      </c>
+      <c r="L210" s="5" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="M210" s="5" t="inlineStr">
+        <is>
+          <t>約115日</t>
+        </is>
+      </c>
+      <c r="N210" s="5" t="inlineStr">
+        <is>
+          <t>広告主新規／WEBより40日以内にキャリアエージェントとの面談実施完了</t>
+        </is>
+      </c>
+      <c r="O210" s="5" t="inlineStr">
+        <is>
+          <t>1世帯2回以上の申込／重複登録・虚偽・入力不備／リスティング違反</t>
+        </is>
+      </c>
+      <c r="P210" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q210" s="5" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="R210" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="S210" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="T210" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="U210" s="5" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="V210" s="5" t="inlineStr">
+        <is>
+          <t>要詳細分析</t>
+        </is>
+      </c>
+      <c r="W210" s="5" t="inlineStr">
+        <is>
+          <t>バックオフィス職特化のオンライン転職支援。確定率25%・EPC56.63円。確定目安が約115日と他案件より大幅に長い</t>
+        </is>
+      </c>
+      <c r="X210" s="5" t="inlineStr">
+        <is>
+          <t>済（写真から入力）</t>
+        </is>
+      </c>
+      <c r="Y210" s="5" t="inlineStr">
+        <is>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+        </is>
+      </c>
+      <c r="Z210" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA210" s="5" t="inlineStr">
+        <is>
+          <t>s00000024822001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="7">
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/Threadsアフィリエイト/A8ネット案件リサーチ.xlsx
+++ b/Threadsアフィリエイト/A8ネット案件リサーチ.xlsx
@@ -4139,7 +4139,8 @@
       </c>
       <c r="Z13" s="5" t="inlineStr">
         <is>
-          <t>訴求しやすいが数字が出ない典型（約234クリックで1件）</t>
+          <t>訴求しやすいが数字が出ない典型（約234クリックで1件）
+【追記】プログラム検索PDFで同一IDを再確認、重複懸念は解消（別プログラムではなく同一案件と確定）</t>
         </is>
       </c>
       <c r="AA13" s="5" t="inlineStr">
@@ -4149,17 +4150,17 @@
       </c>
       <c r="AB13" s="5" t="inlineStr">
         <is>
-          <t>A8.net 即時提携プログラム一覧PDF (2026-09-03/09-05時点)</t>
+          <t>A8.net 即時提携プログラム一覧PDF (2026-09-03/09-05時点) / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC13" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD13" s="5" t="inlineStr">
         <is>
-          <t>s00000026992001（写真で確認、重複プログラムの可能性）</t>
+          <t>s00000026992001</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4213,9 @@
         </is>
       </c>
       <c r="L14" s="7" t="n"/>
-      <c r="M14" s="6" t="n"/>
+      <c r="M14" s="6" t="n">
+        <v>396.82</v>
+      </c>
       <c r="N14" s="8">
         <f>IF(OR(I14="",L14=""),"",I14*L14)</f>
         <v/>
@@ -4274,7 +4277,8 @@
       </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
-          <t>開始から4ヶ月経過して実績なし。14/16件で最も否認条件が少ないが同ジャンルの工場求人ワールドのEPCが低いため優先度は下げる</t>
+          <t>開始から4ヶ月経過して実績なし。14/16件で最も否認条件が少ないが同ジャンルの工場求人ワールドのEPCが低いため優先度は下げる
+【追記】プログラム検索PDFでプログラムID確定、EPC396.82円を確認（確定率は非表示のまま）。対象年齢は既存記載どおり18〜45歳のため、46歳以上向けの候補としては対象外</t>
         </is>
       </c>
       <c r="AA14" s="5" t="inlineStr">
@@ -4284,17 +4288,17 @@
       </c>
       <c r="AB14" s="5" t="inlineStr">
         <is>
-          <t>A8.net 即時提携プログラム一覧PDF (2026-09-03/09-05時点)</t>
+          <t>A8.net 即時提携プログラム一覧PDF (2026-09-03/09-05時点) / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC14" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD14" s="5" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>s00000026996001</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4356,7 @@
       </c>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="6" t="n">
-        <v>27887</v>
+        <v>1146.98</v>
       </c>
       <c r="N15" s="8">
         <f>IF(OR(I15="",L15=""),"",I15*L15)</f>
@@ -4410,12 +4414,12 @@
       </c>
       <c r="Y15" s="5" t="inlineStr">
         <is>
-          <t>判定不能</t>
+          <t>要詳細分析</t>
         </is>
       </c>
       <c r="Z15" s="5" t="inlineStr">
         <is>
-          <t>EPC表示は分母が極小のノイズ。確定率不明で判定不能。適用日の記載に9/8と10/8の矛盾あり要確認</t>
+          <t>プログラム検索PDFで報酬5万円・EPC1,146.98円を確認（旧EPC27,887円は分母極小のノイズ値だったため置き換え）。239件中でも上位級のEPC水準。ただし対象年齢・承認条件は依然未確認のため、詳細ページでの確認が優先度高</t>
         </is>
       </c>
       <c r="AA15" s="5" t="inlineStr">
@@ -4425,17 +4429,17 @@
       </c>
       <c r="AB15" s="5" t="inlineStr">
         <is>
-          <t>A8.net 即時提携プログラム一覧PDF (2026-09-03/09-05時点)</t>
+          <t>A8.net 即時提携プログラム一覧PDF (2026-09-03/09-05時点) / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC15" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD15" s="5" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>s00000024757005</t>
         </is>
       </c>
     </row>
@@ -26511,7 +26515,7 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>株式会社ミライス</t>
+          <t>株式会社ミライユ</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
@@ -26620,7 +26624,8 @@
       <c r="Z172" s="5" t="inlineStr">
         <is>
           <t>タクシードライバー特化。確定率7.69%・EPC13.08円と低め
-【訂正】広告主を「株式会社カラフル」から「株式会社ミライス」に修正（同一プログラムID系列 s00000024432xxx の他3件と広告主が一致するため、当初の記載は誤り）</t>
+【訂正】広告主を「株式会社カラフル」から「株式会社ミライス」に修正（同一プログラムID系列 s00000024432xxx の他3件と広告主が一致するため、当初の記載は誤り）
+【再訂正】広告主名を「株式会社ミライス」から「株式会社ミライユ」に訂正（プログラム検索PDFの実データ抽出で確認。以前の訂正はスクリーンショット読み取りの誤りだった）</t>
         </is>
       </c>
       <c r="AA172" s="5" t="inlineStr">
@@ -26630,12 +26635,12 @@
       </c>
       <c r="AB172" s="5" t="inlineStr">
         <is>
-          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット） / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC172" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD172" s="5" t="inlineStr">
@@ -30345,7 +30350,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>株式会社ミライス</t>
+          <t>株式会社ミライユ</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -30453,7 +30458,8 @@
       </c>
       <c r="Z199" s="5" t="inlineStr">
         <is>
-          <t>同一広告主のドライバーズワーク（既存行）と系列。確定率3.7%と低め、EPC21.43円</t>
+          <t>同一広告主のドライバーズワーク（既存行）と系列。確定率3.7%と低め、EPC21.43円
+【再訂正】広告主名を「株式会社ミライス」から「株式会社ミライユ」に訂正（プログラム検索PDFの実データ抽出で確認。以前の訂正はスクリーンショット読み取りの誤りだった）</t>
         </is>
       </c>
       <c r="AA199" s="5" t="inlineStr">
@@ -30463,12 +30469,12 @@
       </c>
       <c r="AB199" s="5" t="inlineStr">
         <is>
-          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット） / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC199" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD199" s="5" t="inlineStr">
@@ -34446,7 +34452,7 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>株式会社ミライス</t>
+          <t>株式会社ミライユ</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -34552,7 +34558,8 @@
       </c>
       <c r="Z228" s="5" t="inlineStr">
         <is>
-          <t>同一広告主の別ジャンル版（既存行のタクシー版）に対しトラック特化版。EPC9.66円と低め、確定率は非表示</t>
+          <t>同一広告主の別ジャンル版（既存行のタクシー版）に対しトラック特化版。EPC9.66円と低め、確定率は非表示
+【再訂正】広告主名を「株式会社ミライス」から「株式会社ミライユ」に訂正（プログラム検索PDFの実データ抽出で確認。以前の訂正はスクリーンショット読み取りの誤りだった）</t>
         </is>
       </c>
       <c r="AA228" s="5" t="inlineStr">
@@ -34562,12 +34569,12 @@
       </c>
       <c r="AB228" s="5" t="inlineStr">
         <is>
-          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット） / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC228" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD228" s="5" t="inlineStr">
@@ -34587,7 +34594,7 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>株式会社ミライス</t>
+          <t>株式会社ミライユ</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
@@ -34695,7 +34702,8 @@
       </c>
       <c r="Z229" s="5" t="inlineStr">
         <is>
-          <t>同一広告主ミライス系列の警備員特化版。確定率16.98%・EPC42.96円</t>
+          <t>同一広告主ミライス系列の警備員特化版。確定率16.98%・EPC42.96円
+【再訂正】広告主名を「株式会社ミライス」から「株式会社ミライユ」に訂正（プログラム検索PDFの実データ抽出で確認。以前の訂正はスクリーンショット読み取りの誤りだった）</t>
         </is>
       </c>
       <c r="AA229" s="5" t="inlineStr">
@@ -34705,12 +34713,12 @@
       </c>
       <c r="AB229" s="5" t="inlineStr">
         <is>
-          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット）</t>
+          <t>A8.netプログラム詳細画面（ユーザー提供スクリーンショット） / A8.netプログラム検索結果PDF（就職・転職カテゴリ、報酬額順エクスポート）</t>
         </is>
       </c>
       <c r="AC229" s="5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD229" s="5" t="inlineStr">
